--- a/database/event/8064/event_8064_evp_summary.xlsx
+++ b/database/event/8064/event_8064_evp_summary.xlsx
@@ -499,7 +499,7 @@
         <v>9.190899999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>3.8235</v>
       </c>
       <c r="D2" t="n">
         <v>3.2916</v>
@@ -545,7 +545,7 @@
         <v>7.6692</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>3.1904</v>
       </c>
       <c r="D3" t="n">
         <v>2.6768</v>
@@ -591,7 +591,7 @@
         <v>7.6367</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>3.1769</v>
       </c>
       <c r="D4" t="n">
         <v>2.6637</v>
@@ -637,7 +637,7 @@
         <v>7.4158</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>3.085</v>
       </c>
       <c r="D5" t="n">
         <v>2.5745</v>
@@ -683,7 +683,7 @@
         <v>7.2569</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>3.0189</v>
       </c>
       <c r="D6" t="n">
         <v>2.5103</v>
@@ -729,7 +729,7 @@
         <v>6.8383</v>
       </c>
       <c r="C7" t="n">
-        <v>0</v>
+        <v>2.8448</v>
       </c>
       <c r="D7" t="n">
         <v>2.3412</v>
@@ -775,7 +775,7 @@
         <v>6.2366</v>
       </c>
       <c r="C8" t="n">
-        <v>0</v>
+        <v>2.5945</v>
       </c>
       <c r="D8" t="n">
         <v>2.0981</v>
@@ -821,7 +821,7 @@
         <v>5.7824</v>
       </c>
       <c r="C9" t="n">
-        <v>0</v>
+        <v>2.4055</v>
       </c>
       <c r="D9" t="n">
         <v>1.9146</v>
@@ -867,7 +867,7 @@
         <v>5.7399</v>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>2.3878</v>
       </c>
       <c r="D10" t="n">
         <v>1.8974</v>
@@ -913,7 +913,7 @@
         <v>5.1746</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>2.1527</v>
       </c>
       <c r="D11" t="n">
         <v>1.6691</v>
@@ -959,7 +959,7 @@
         <v>4.2207</v>
       </c>
       <c r="C12" t="n">
-        <v>0</v>
+        <v>1.7558</v>
       </c>
       <c r="D12" t="n">
         <v>1.2837</v>
@@ -1005,7 +1005,7 @@
         <v>3.9435</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>1.6405</v>
       </c>
       <c r="D13" t="n">
         <v>1.1717</v>
@@ -1051,7 +1051,7 @@
         <v>3.7764</v>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>1.571</v>
       </c>
       <c r="D14" t="n">
         <v>1.1042</v>
@@ -1097,7 +1097,7 @@
         <v>3.7612</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>1.5647</v>
       </c>
       <c r="D15" t="n">
         <v>1.0981</v>
@@ -1143,7 +1143,7 @@
         <v>3.694</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>1.5367</v>
       </c>
       <c r="D16" t="n">
         <v>1.0709</v>
@@ -1189,7 +1189,7 @@
         <v>3.4585</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.4388</v>
       </c>
       <c r="D17" t="n">
         <v>0.9758</v>
@@ -1235,7 +1235,7 @@
         <v>3.4392</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.4307</v>
       </c>
       <c r="D18" t="n">
         <v>0.968</v>
@@ -1281,7 +1281,7 @@
         <v>3.3796</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.4059</v>
       </c>
       <c r="D19" t="n">
         <v>0.9439</v>
@@ -1327,7 +1327,7 @@
         <v>3.3398</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>1.3894</v>
       </c>
       <c r="D20" t="n">
         <v>0.9278</v>
@@ -1373,7 +1373,7 @@
         <v>3.2716</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>1.361</v>
       </c>
       <c r="D21" t="n">
         <v>0.9003</v>
@@ -1419,7 +1419,7 @@
         <v>3.2426</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>1.3489</v>
       </c>
       <c r="D22" t="n">
         <v>0.8885999999999999</v>
@@ -1465,7 +1465,7 @@
         <v>3.1417</v>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>1.307</v>
       </c>
       <c r="D23" t="n">
         <v>0.8478</v>
@@ -1511,7 +1511,7 @@
         <v>3.0745</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>1.279</v>
       </c>
       <c r="D24" t="n">
         <v>0.8207</v>
@@ -1557,7 +1557,7 @@
         <v>3.0147</v>
       </c>
       <c r="C25" t="n">
-        <v>0</v>
+        <v>1.2541</v>
       </c>
       <c r="D25" t="n">
         <v>0.7965</v>
@@ -1603,7 +1603,7 @@
         <v>2.9512</v>
       </c>
       <c r="C26" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="D26" t="n">
         <v>0.7709</v>
@@ -1649,7 +1649,7 @@
         <v>2.7155</v>
       </c>
       <c r="C27" t="n">
-        <v>0</v>
+        <v>1.1297</v>
       </c>
       <c r="D27" t="n">
         <v>0.6756</v>
@@ -1695,7 +1695,7 @@
         <v>2.6569</v>
       </c>
       <c r="C28" t="n">
-        <v>0</v>
+        <v>1.1053</v>
       </c>
       <c r="D28" t="n">
         <v>0.652</v>
@@ -1741,7 +1741,7 @@
         <v>2.488</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>1.035</v>
       </c>
       <c r="D29" t="n">
         <v>0.5837</v>
@@ -1787,7 +1787,7 @@
         <v>2.4501</v>
       </c>
       <c r="C30" t="n">
-        <v>0</v>
+        <v>1.0193</v>
       </c>
       <c r="D30" t="n">
         <v>0.5684</v>
@@ -1833,7 +1833,7 @@
         <v>2.3264</v>
       </c>
       <c r="C31" t="n">
-        <v>0</v>
+        <v>0.9678</v>
       </c>
       <c r="D31" t="n">
         <v>0.5185</v>
@@ -1879,7 +1879,7 @@
         <v>2.2835</v>
       </c>
       <c r="C32" t="n">
-        <v>0</v>
+        <v>0.9499</v>
       </c>
       <c r="D32" t="n">
         <v>0.5011</v>
@@ -1925,7 +1925,7 @@
         <v>1.9083</v>
       </c>
       <c r="C33" t="n">
-        <v>0</v>
+        <v>0.7939000000000001</v>
       </c>
       <c r="D33" t="n">
         <v>0.3495</v>
@@ -1971,7 +1971,7 @@
         <v>1.8875</v>
       </c>
       <c r="C34" t="n">
-        <v>0</v>
+        <v>0.7852</v>
       </c>
       <c r="D34" t="n">
         <v>0.3411</v>
@@ -2017,7 +2017,7 @@
         <v>1.7678</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="D35" t="n">
         <v>0.2928</v>
@@ -2063,7 +2063,7 @@
         <v>1.6475</v>
       </c>
       <c r="C36" t="n">
-        <v>0</v>
+        <v>0.6854</v>
       </c>
       <c r="D36" t="n">
         <v>0.2442</v>
@@ -2109,7 +2109,7 @@
         <v>1.4713</v>
       </c>
       <c r="C37" t="n">
-        <v>0</v>
+        <v>0.6121</v>
       </c>
       <c r="D37" t="n">
         <v>0.173</v>
@@ -2155,7 +2155,7 @@
         <v>1.4188</v>
       </c>
       <c r="C38" t="n">
-        <v>0</v>
+        <v>0.5901999999999999</v>
       </c>
       <c r="D38" t="n">
         <v>0.1518</v>
@@ -2201,7 +2201,7 @@
         <v>1.3354</v>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>0.5555</v>
       </c>
       <c r="D39" t="n">
         <v>0.1181</v>
@@ -2247,7 +2247,7 @@
         <v>1.1939</v>
       </c>
       <c r="C40" t="n">
-        <v>0</v>
+        <v>0.4967</v>
       </c>
       <c r="D40" t="n">
         <v>0.0609</v>
@@ -2293,7 +2293,7 @@
         <v>1.1853</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>0.4931</v>
       </c>
       <c r="D41" t="n">
         <v>0.0575</v>
@@ -2339,7 +2339,7 @@
         <v>1.1649</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.4846</v>
       </c>
       <c r="D42" t="n">
         <v>0.0492</v>
@@ -2385,7 +2385,7 @@
         <v>1.1079</v>
       </c>
       <c r="C43" t="n">
-        <v>0</v>
+        <v>0.4609</v>
       </c>
       <c r="D43" t="n">
         <v>0.0262</v>
@@ -2431,7 +2431,7 @@
         <v>1.0783</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>0.4486</v>
       </c>
       <c r="D44" t="n">
         <v>0.0142</v>
@@ -2477,7 +2477,7 @@
         <v>1.0692</v>
       </c>
       <c r="C45" t="n">
-        <v>0</v>
+        <v>0.4448</v>
       </c>
       <c r="D45" t="n">
         <v>0.0106</v>
@@ -2523,7 +2523,7 @@
         <v>1.0392</v>
       </c>
       <c r="C46" t="n">
-        <v>0</v>
+        <v>0.4323</v>
       </c>
       <c r="D46" t="n">
         <v>-0.0015</v>
@@ -2569,7 +2569,7 @@
         <v>1.0351</v>
       </c>
       <c r="C47" t="n">
-        <v>0</v>
+        <v>0.4306</v>
       </c>
       <c r="D47" t="n">
         <v>-0.0032</v>
@@ -2615,7 +2615,7 @@
         <v>0.8267</v>
       </c>
       <c r="C48" t="n">
-        <v>0</v>
+        <v>0.3439</v>
       </c>
       <c r="D48" t="n">
         <v>-0.08740000000000001</v>
@@ -2661,7 +2661,7 @@
         <v>0.7959000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>0</v>
+        <v>0.3311</v>
       </c>
       <c r="D49" t="n">
         <v>-0.0998</v>
@@ -2707,7 +2707,7 @@
         <v>0.6839</v>
       </c>
       <c r="C50" t="n">
-        <v>0</v>
+        <v>0.2845</v>
       </c>
       <c r="D50" t="n">
         <v>-0.1451</v>
@@ -2753,7 +2753,7 @@
         <v>0.4695</v>
       </c>
       <c r="C51" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="D51" t="n">
         <v>-0.2317</v>
@@ -2799,7 +2799,7 @@
         <v>0.361</v>
       </c>
       <c r="C52" t="n">
-        <v>0</v>
+        <v>0.1502</v>
       </c>
       <c r="D52" t="n">
         <v>-0.2755</v>
@@ -2845,7 +2845,7 @@
         <v>0.1958</v>
       </c>
       <c r="C53" t="n">
-        <v>0</v>
+        <v>0.0815</v>
       </c>
       <c r="D53" t="n">
         <v>-0.3423</v>
@@ -2891,7 +2891,7 @@
         <v>0.1791</v>
       </c>
       <c r="C54" t="n">
-        <v>0</v>
+        <v>0.0745</v>
       </c>
       <c r="D54" t="n">
         <v>-0.349</v>
@@ -2937,7 +2937,7 @@
         <v>0.1399</v>
       </c>
       <c r="C55" t="n">
-        <v>0</v>
+        <v>0.0582</v>
       </c>
       <c r="D55" t="n">
         <v>-0.3648</v>
@@ -2983,7 +2983,7 @@
         <v>0.1081</v>
       </c>
       <c r="C56" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="D56" t="n">
         <v>-0.3777</v>
@@ -3029,7 +3029,7 @@
         <v>-0.1889</v>
       </c>
       <c r="C57" t="n">
-        <v>-0</v>
+        <v>-0.0786</v>
       </c>
       <c r="D57" t="n">
         <v>-0.4977</v>
@@ -3075,7 +3075,7 @@
         <v>-0.1928</v>
       </c>
       <c r="C58" t="n">
-        <v>-0</v>
+        <v>-0.08019999999999999</v>
       </c>
       <c r="D58" t="n">
         <v>-0.4992</v>
@@ -3121,7 +3121,7 @@
         <v>-0.3982</v>
       </c>
       <c r="C59" t="n">
-        <v>-0</v>
+        <v>-0.1657</v>
       </c>
       <c r="D59" t="n">
         <v>-0.5822000000000001</v>
@@ -3167,7 +3167,7 @@
         <v>-0.4294</v>
       </c>
       <c r="C60" t="n">
-        <v>-0</v>
+        <v>-0.1786</v>
       </c>
       <c r="D60" t="n">
         <v>-0.5948</v>
@@ -3213,7 +3213,7 @@
         <v>-0.4552</v>
       </c>
       <c r="C61" t="n">
-        <v>-0</v>
+        <v>-0.1894</v>
       </c>
       <c r="D61" t="n">
         <v>-0.6052999999999999</v>
@@ -3259,7 +3259,7 @@
         <v>-0.5242</v>
       </c>
       <c r="C62" t="n">
-        <v>-0</v>
+        <v>-0.2181</v>
       </c>
       <c r="D62" t="n">
         <v>-0.6331</v>
@@ -3305,7 +3305,7 @@
         <v>-0.5437</v>
       </c>
       <c r="C63" t="n">
-        <v>-0</v>
+        <v>-0.2262</v>
       </c>
       <c r="D63" t="n">
         <v>-0.641</v>
@@ -3351,7 +3351,7 @@
         <v>-0.6501</v>
       </c>
       <c r="C64" t="n">
-        <v>-0</v>
+        <v>-0.2704</v>
       </c>
       <c r="D64" t="n">
         <v>-0.6840000000000001</v>
@@ -3397,7 +3397,7 @@
         <v>-0.6634</v>
       </c>
       <c r="C65" t="n">
-        <v>-0</v>
+        <v>-0.276</v>
       </c>
       <c r="D65" t="n">
         <v>-0.6894</v>
@@ -3443,7 +3443,7 @@
         <v>-1.0085</v>
       </c>
       <c r="C66" t="n">
-        <v>-0</v>
+        <v>-0.4195</v>
       </c>
       <c r="D66" t="n">
         <v>-0.8288</v>
@@ -3489,7 +3489,7 @@
         <v>-1.0303</v>
       </c>
       <c r="C67" t="n">
-        <v>-0</v>
+        <v>-0.4286</v>
       </c>
       <c r="D67" t="n">
         <v>-0.8376</v>
@@ -3535,7 +3535,7 @@
         <v>-1.2411</v>
       </c>
       <c r="C68" t="n">
-        <v>-0</v>
+        <v>-0.5163</v>
       </c>
       <c r="D68" t="n">
         <v>-0.9227</v>
@@ -3581,7 +3581,7 @@
         <v>-1.3548</v>
       </c>
       <c r="C69" t="n">
-        <v>-0</v>
+        <v>-0.5636</v>
       </c>
       <c r="D69" t="n">
         <v>-0.9687</v>
@@ -3627,7 +3627,7 @@
         <v>-1.6979</v>
       </c>
       <c r="C70" t="n">
-        <v>-0</v>
+        <v>-0.7063</v>
       </c>
       <c r="D70" t="n">
         <v>-1.1073</v>
@@ -3673,7 +3673,7 @@
         <v>-1.888</v>
       </c>
       <c r="C71" t="n">
-        <v>-0</v>
+        <v>-0.7854</v>
       </c>
       <c r="D71" t="n">
         <v>-1.1841</v>
@@ -3719,7 +3719,7 @@
         <v>-2.1256</v>
       </c>
       <c r="C72" t="n">
-        <v>-0</v>
+        <v>-0.8843</v>
       </c>
       <c r="D72" t="n">
         <v>-1.2801</v>
@@ -3765,7 +3765,7 @@
         <v>-2.1361</v>
       </c>
       <c r="C73" t="n">
-        <v>-0</v>
+        <v>-0.8885999999999999</v>
       </c>
       <c r="D73" t="n">
         <v>-1.2843</v>
@@ -3811,7 +3811,7 @@
         <v>-2.2602</v>
       </c>
       <c r="C74" t="n">
-        <v>-0</v>
+        <v>-0.9403</v>
       </c>
       <c r="D74" t="n">
         <v>-1.3344</v>
@@ -3857,7 +3857,7 @@
         <v>-2.4146</v>
       </c>
       <c r="C75" t="n">
-        <v>-0</v>
+        <v>-1.0045</v>
       </c>
       <c r="D75" t="n">
         <v>-1.3968</v>
@@ -3903,7 +3903,7 @@
         <v>-2.607</v>
       </c>
       <c r="C76" t="n">
-        <v>-0</v>
+        <v>-1.0845</v>
       </c>
       <c r="D76" t="n">
         <v>-1.4745</v>
@@ -3949,7 +3949,7 @@
         <v>-2.6799</v>
       </c>
       <c r="C77" t="n">
-        <v>-0</v>
+        <v>-1.1149</v>
       </c>
       <c r="D77" t="n">
         <v>-1.504</v>
@@ -3995,7 +3995,7 @@
         <v>-2.708</v>
       </c>
       <c r="C78" t="n">
-        <v>-0</v>
+        <v>-1.1265</v>
       </c>
       <c r="D78" t="n">
         <v>-1.5153</v>
@@ -4041,7 +4041,7 @@
         <v>-3.2406</v>
       </c>
       <c r="C79" t="n">
-        <v>-0</v>
+        <v>-1.3481</v>
       </c>
       <c r="D79" t="n">
         <v>-1.7305</v>
@@ -4087,7 +4087,7 @@
         <v>-4.9765</v>
       </c>
       <c r="C80" t="n">
-        <v>-0</v>
+        <v>-2.0702</v>
       </c>
       <c r="D80" t="n">
         <v>-2.4318</v>
@@ -4133,7 +4133,7 @@
         <v>-5.4475</v>
       </c>
       <c r="C81" t="n">
-        <v>-0</v>
+        <v>-2.2662</v>
       </c>
       <c r="D81" t="n">
         <v>-2.622</v>

--- a/database/event/8064/event_8064_evp_summary.xlsx
+++ b/database/event/8064/event_8064_evp_summary.xlsx
@@ -502,7 +502,7 @@
         <v>3.8235</v>
       </c>
       <c r="D2" t="n">
-        <v>3.2916</v>
+        <v>3.2177</v>
       </c>
       <c r="E2" t="n">
         <v>9.190899999999999</v>
@@ -542,25 +542,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.6692</v>
+        <v>7.6599</v>
       </c>
       <c r="C3" t="n">
-        <v>3.1904</v>
+        <v>3.1866</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6768</v>
+        <v>2.6078</v>
       </c>
       <c r="E3" t="n">
-        <v>7.6692</v>
+        <v>7.6599</v>
       </c>
       <c r="F3" t="n">
-        <v>2.4906</v>
+        <v>2.4813</v>
       </c>
       <c r="G3" t="n">
         <v>5.1786</v>
       </c>
       <c r="H3" t="n">
-        <v>2.4906</v>
+        <v>2.4813</v>
       </c>
       <c r="I3" t="n">
         <v>2.5022</v>
@@ -594,7 +594,7 @@
         <v>3.1769</v>
       </c>
       <c r="D4" t="n">
-        <v>2.6637</v>
+        <v>2.5986</v>
       </c>
       <c r="E4" t="n">
         <v>7.6367</v>
@@ -634,25 +634,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.4158</v>
+        <v>7.4015</v>
       </c>
       <c r="C5" t="n">
-        <v>3.085</v>
+        <v>3.0791</v>
       </c>
       <c r="D5" t="n">
-        <v>2.5745</v>
+        <v>2.5048</v>
       </c>
       <c r="E5" t="n">
-        <v>7.4158</v>
+        <v>7.4015</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3219</v>
+        <v>5.3076</v>
       </c>
       <c r="G5" t="n">
         <v>2.0939</v>
       </c>
       <c r="H5" t="n">
-        <v>6.0417</v>
+        <v>6.0192</v>
       </c>
       <c r="I5" t="n">
         <v>6.0698</v>
@@ -680,25 +680,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7.2569</v>
+        <v>7.2442</v>
       </c>
       <c r="C6" t="n">
-        <v>3.0189</v>
+        <v>3.0136</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5103</v>
+        <v>2.4422</v>
       </c>
       <c r="E6" t="n">
-        <v>7.2569</v>
+        <v>7.2442</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4118</v>
+        <v>3.3991</v>
       </c>
       <c r="G6" t="n">
         <v>3.8451</v>
       </c>
       <c r="H6" t="n">
-        <v>3.4118</v>
+        <v>3.3991</v>
       </c>
       <c r="I6" t="n">
         <v>3.4277</v>
@@ -732,7 +732,7 @@
         <v>2.8448</v>
       </c>
       <c r="D7" t="n">
-        <v>2.3412</v>
+        <v>2.2805</v>
       </c>
       <c r="E7" t="n">
         <v>6.8383</v>
@@ -778,7 +778,7 @@
         <v>2.5945</v>
       </c>
       <c r="D8" t="n">
-        <v>2.0981</v>
+        <v>2.0408</v>
       </c>
       <c r="E8" t="n">
         <v>6.2366</v>
@@ -824,7 +824,7 @@
         <v>2.4055</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9146</v>
+        <v>1.8598</v>
       </c>
       <c r="E9" t="n">
         <v>5.7824</v>
@@ -864,25 +864,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.7399</v>
+        <v>5.7249</v>
       </c>
       <c r="C10" t="n">
-        <v>2.3878</v>
+        <v>2.3816</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8974</v>
+        <v>1.8369</v>
       </c>
       <c r="E10" t="n">
-        <v>5.7399</v>
+        <v>5.7249</v>
       </c>
       <c r="F10" t="n">
-        <v>4.0379</v>
+        <v>4.0229</v>
       </c>
       <c r="G10" t="n">
         <v>1.702</v>
       </c>
       <c r="H10" t="n">
-        <v>4.0379</v>
+        <v>4.0229</v>
       </c>
       <c r="I10" t="n">
         <v>4.0567</v>
@@ -916,7 +916,7 @@
         <v>2.1527</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6691</v>
+        <v>1.6177</v>
       </c>
       <c r="E11" t="n">
         <v>5.1746</v>
@@ -962,7 +962,7 @@
         <v>1.7558</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2837</v>
+        <v>1.2376</v>
       </c>
       <c r="E12" t="n">
         <v>4.2207</v>
@@ -1008,7 +1008,7 @@
         <v>1.6405</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1717</v>
+        <v>1.1272</v>
       </c>
       <c r="E13" t="n">
         <v>3.9435</v>
@@ -1054,7 +1054,7 @@
         <v>1.571</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1042</v>
+        <v>1.0606</v>
       </c>
       <c r="E14" t="n">
         <v>3.7764</v>
@@ -1094,25 +1094,25 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7612</v>
+        <v>3.7573</v>
       </c>
       <c r="C15" t="n">
-        <v>1.5647</v>
+        <v>1.5631</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0981</v>
+        <v>1.053</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7612</v>
+        <v>3.7573</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0318</v>
+        <v>1.0279</v>
       </c>
       <c r="G15" t="n">
         <v>2.7294</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0318</v>
+        <v>1.0279</v>
       </c>
       <c r="I15" t="n">
         <v>1.0366</v>
@@ -1146,7 +1146,7 @@
         <v>1.5367</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0709</v>
+        <v>1.0278</v>
       </c>
       <c r="E16" t="n">
         <v>3.694</v>
@@ -1186,25 +1186,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.4585</v>
+        <v>3.4453</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4388</v>
+        <v>1.4333</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9758</v>
+        <v>0.9287</v>
       </c>
       <c r="E17" t="n">
-        <v>3.4585</v>
+        <v>3.4453</v>
       </c>
       <c r="F17" t="n">
-        <v>3.5365</v>
+        <v>3.5233</v>
       </c>
       <c r="G17" t="n">
         <v>-0.078</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5365</v>
+        <v>3.5233</v>
       </c>
       <c r="I17" t="n">
         <v>3.5529</v>
@@ -1238,7 +1238,7 @@
         <v>1.4307</v>
       </c>
       <c r="D18" t="n">
-        <v>0.968</v>
+        <v>0.9263</v>
       </c>
       <c r="E18" t="n">
         <v>3.4392</v>
@@ -1284,7 +1284,7 @@
         <v>1.4059</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9439</v>
+        <v>0.9025</v>
       </c>
       <c r="E19" t="n">
         <v>3.3796</v>
@@ -1330,7 +1330,7 @@
         <v>1.3894</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9278</v>
+        <v>0.8867</v>
       </c>
       <c r="E20" t="n">
         <v>3.3398</v>
@@ -1376,7 +1376,7 @@
         <v>1.361</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9003</v>
+        <v>0.8595</v>
       </c>
       <c r="E21" t="n">
         <v>3.2716</v>
@@ -1422,7 +1422,7 @@
         <v>1.3489</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8885999999999999</v>
+        <v>0.8479</v>
       </c>
       <c r="E22" t="n">
         <v>3.2426</v>
@@ -1468,7 +1468,7 @@
         <v>1.307</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8478</v>
+        <v>0.8077</v>
       </c>
       <c r="E23" t="n">
         <v>3.1417</v>
@@ -1514,7 +1514,7 @@
         <v>1.279</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8207</v>
+        <v>0.781</v>
       </c>
       <c r="E24" t="n">
         <v>3.0745</v>
@@ -1560,7 +1560,7 @@
         <v>1.2541</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7965</v>
+        <v>0.7571</v>
       </c>
       <c r="E25" t="n">
         <v>3.0147</v>
@@ -1600,25 +1600,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.9512</v>
+        <v>2.9478</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2277</v>
+        <v>1.2263</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7709</v>
+        <v>0.7305</v>
       </c>
       <c r="E26" t="n">
-        <v>2.9512</v>
+        <v>2.9478</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9064</v>
+        <v>0.903</v>
       </c>
       <c r="G26" t="n">
         <v>2.0448</v>
       </c>
       <c r="H26" t="n">
-        <v>0.9064</v>
+        <v>0.903</v>
       </c>
       <c r="I26" t="n">
         <v>0.9106</v>
@@ -1646,25 +1646,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2.7155</v>
+        <v>2.7138</v>
       </c>
       <c r="C27" t="n">
-        <v>1.1297</v>
+        <v>1.129</v>
       </c>
       <c r="D27" t="n">
-        <v>0.6756</v>
+        <v>0.6373</v>
       </c>
       <c r="E27" t="n">
-        <v>2.7155</v>
+        <v>2.7138</v>
       </c>
       <c r="F27" t="n">
-        <v>0.4362</v>
+        <v>0.4345</v>
       </c>
       <c r="G27" t="n">
         <v>2.2793</v>
       </c>
       <c r="H27" t="n">
-        <v>0.4362</v>
+        <v>0.4345</v>
       </c>
       <c r="I27" t="n">
         <v>0.4382</v>
@@ -1698,7 +1698,7 @@
         <v>1.1053</v>
       </c>
       <c r="D28" t="n">
-        <v>0.652</v>
+        <v>0.6146</v>
       </c>
       <c r="E28" t="n">
         <v>2.6569</v>
@@ -1744,7 +1744,7 @@
         <v>1.035</v>
       </c>
       <c r="D29" t="n">
-        <v>0.5837</v>
+        <v>0.5473</v>
       </c>
       <c r="E29" t="n">
         <v>2.488</v>
@@ -1784,25 +1784,25 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.4501</v>
+        <v>2.4401</v>
       </c>
       <c r="C30" t="n">
-        <v>1.0193</v>
+        <v>1.0151</v>
       </c>
       <c r="D30" t="n">
-        <v>0.5684</v>
+        <v>0.5282</v>
       </c>
       <c r="E30" t="n">
-        <v>2.4501</v>
+        <v>2.4401</v>
       </c>
       <c r="F30" t="n">
-        <v>2.6785</v>
+        <v>2.6685</v>
       </c>
       <c r="G30" t="n">
         <v>-0.2284</v>
       </c>
       <c r="H30" t="n">
-        <v>2.6785</v>
+        <v>2.6685</v>
       </c>
       <c r="I30" t="n">
         <v>2.691</v>
@@ -1836,7 +1836,7 @@
         <v>0.9678</v>
       </c>
       <c r="D31" t="n">
-        <v>0.5185</v>
+        <v>0.4829</v>
       </c>
       <c r="E31" t="n">
         <v>2.3264</v>
@@ -1882,7 +1882,7 @@
         <v>0.9499</v>
       </c>
       <c r="D32" t="n">
-        <v>0.5011</v>
+        <v>0.4658</v>
       </c>
       <c r="E32" t="n">
         <v>2.2835</v>
@@ -1928,7 +1928,7 @@
         <v>0.7939000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>0.3495</v>
+        <v>0.3164</v>
       </c>
       <c r="E33" t="n">
         <v>1.9083</v>
@@ -1974,7 +1974,7 @@
         <v>0.7852</v>
       </c>
       <c r="D34" t="n">
-        <v>0.3411</v>
+        <v>0.3081</v>
       </c>
       <c r="E34" t="n">
         <v>1.8875</v>
@@ -2020,7 +2020,7 @@
         <v>0.7354000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>0.2928</v>
+        <v>0.2604</v>
       </c>
       <c r="E35" t="n">
         <v>1.7678</v>
@@ -2066,7 +2066,7 @@
         <v>0.6854</v>
       </c>
       <c r="D36" t="n">
-        <v>0.2442</v>
+        <v>0.2125</v>
       </c>
       <c r="E36" t="n">
         <v>1.6475</v>
@@ -2112,7 +2112,7 @@
         <v>0.6121</v>
       </c>
       <c r="D37" t="n">
-        <v>0.173</v>
+        <v>0.1423</v>
       </c>
       <c r="E37" t="n">
         <v>1.4713</v>
@@ -2158,7 +2158,7 @@
         <v>0.5901999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1518</v>
+        <v>0.1213</v>
       </c>
       <c r="E38" t="n">
         <v>1.4188</v>
@@ -2204,7 +2204,7 @@
         <v>0.5555</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1181</v>
+        <v>0.0881</v>
       </c>
       <c r="E39" t="n">
         <v>1.3354</v>
@@ -2250,7 +2250,7 @@
         <v>0.4967</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0609</v>
+        <v>0.0317</v>
       </c>
       <c r="E40" t="n">
         <v>1.1939</v>
@@ -2296,7 +2296,7 @@
         <v>0.4931</v>
       </c>
       <c r="D41" t="n">
-        <v>0.0575</v>
+        <v>0.0283</v>
       </c>
       <c r="E41" t="n">
         <v>1.1853</v>
@@ -2342,7 +2342,7 @@
         <v>0.4846</v>
       </c>
       <c r="D42" t="n">
-        <v>0.0492</v>
+        <v>0.0202</v>
       </c>
       <c r="E42" t="n">
         <v>1.1649</v>
@@ -2388,7 +2388,7 @@
         <v>0.4609</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0262</v>
+        <v>-0.0025</v>
       </c>
       <c r="E43" t="n">
         <v>1.1079</v>
@@ -2434,7 +2434,7 @@
         <v>0.4486</v>
       </c>
       <c r="D44" t="n">
-        <v>0.0142</v>
+        <v>-0.0143</v>
       </c>
       <c r="E44" t="n">
         <v>1.0783</v>
@@ -2480,7 +2480,7 @@
         <v>0.4448</v>
       </c>
       <c r="D45" t="n">
-        <v>0.0106</v>
+        <v>-0.0179</v>
       </c>
       <c r="E45" t="n">
         <v>1.0692</v>
@@ -2526,7 +2526,7 @@
         <v>0.4323</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.0015</v>
+        <v>-0.0299</v>
       </c>
       <c r="E46" t="n">
         <v>1.0392</v>
@@ -2572,7 +2572,7 @@
         <v>0.4306</v>
       </c>
       <c r="D47" t="n">
-        <v>-0.0032</v>
+        <v>-0.0315</v>
       </c>
       <c r="E47" t="n">
         <v>1.0351</v>
@@ -2612,25 +2612,25 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8267</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>0.3439</v>
+        <v>0.3412</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.08740000000000001</v>
+        <v>-0.1172</v>
       </c>
       <c r="E48" t="n">
-        <v>0.8267</v>
+        <v>0.8201000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>1.7682</v>
+        <v>1.7616</v>
       </c>
       <c r="G48" t="n">
         <v>-0.9415</v>
       </c>
       <c r="H48" t="n">
-        <v>1.7682</v>
+        <v>1.7616</v>
       </c>
       <c r="I48" t="n">
         <v>1.7764</v>
@@ -2664,7 +2664,7 @@
         <v>0.3311</v>
       </c>
       <c r="D49" t="n">
-        <v>-0.0998</v>
+        <v>-0.1268</v>
       </c>
       <c r="E49" t="n">
         <v>0.7959000000000001</v>
@@ -2710,7 +2710,7 @@
         <v>0.2845</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.1451</v>
+        <v>-0.1714</v>
       </c>
       <c r="E50" t="n">
         <v>0.6839</v>
@@ -2756,7 +2756,7 @@
         <v>0.1953</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.2317</v>
+        <v>-0.2569</v>
       </c>
       <c r="E51" t="n">
         <v>0.4695</v>
@@ -2802,7 +2802,7 @@
         <v>0.1502</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.2755</v>
+        <v>-0.3001</v>
       </c>
       <c r="E52" t="n">
         <v>0.361</v>
@@ -2842,25 +2842,25 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.1958</v>
+        <v>0.1903</v>
       </c>
       <c r="C53" t="n">
-        <v>0.0815</v>
+        <v>0.07920000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.3423</v>
+        <v>-0.3681</v>
       </c>
       <c r="E53" t="n">
-        <v>0.1958</v>
+        <v>0.1903</v>
       </c>
       <c r="F53" t="n">
-        <v>1.4762</v>
+        <v>1.4707</v>
       </c>
       <c r="G53" t="n">
         <v>-1.2804</v>
       </c>
       <c r="H53" t="n">
-        <v>1.4762</v>
+        <v>1.4707</v>
       </c>
       <c r="I53" t="n">
         <v>1.483</v>
@@ -2894,7 +2894,7 @@
         <v>0.0745</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.349</v>
+        <v>-0.3726</v>
       </c>
       <c r="E54" t="n">
         <v>0.1791</v>
@@ -2940,7 +2940,7 @@
         <v>0.0582</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.3648</v>
+        <v>-0.3882</v>
       </c>
       <c r="E55" t="n">
         <v>0.1399</v>
@@ -2986,7 +2986,7 @@
         <v>0.045</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.3777</v>
+        <v>-0.4008</v>
       </c>
       <c r="E56" t="n">
         <v>0.1081</v>
@@ -3032,7 +3032,7 @@
         <v>-0.0786</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4977</v>
+        <v>-0.5192</v>
       </c>
       <c r="E57" t="n">
         <v>-0.1889</v>
@@ -3078,7 +3078,7 @@
         <v>-0.08019999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4992</v>
+        <v>-0.5207000000000001</v>
       </c>
       <c r="E58" t="n">
         <v>-0.1928</v>
@@ -3124,7 +3124,7 @@
         <v>-0.1657</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.5822000000000001</v>
+        <v>-0.6026</v>
       </c>
       <c r="E59" t="n">
         <v>-0.3982</v>
@@ -3170,7 +3170,7 @@
         <v>-0.1786</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.5948</v>
+        <v>-0.615</v>
       </c>
       <c r="E60" t="n">
         <v>-0.4294</v>
@@ -3216,7 +3216,7 @@
         <v>-0.1894</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.6052999999999999</v>
+        <v>-0.6253</v>
       </c>
       <c r="E61" t="n">
         <v>-0.4552</v>
@@ -3262,7 +3262,7 @@
         <v>-0.2181</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.6331</v>
+        <v>-0.6528</v>
       </c>
       <c r="E62" t="n">
         <v>-0.5242</v>
@@ -3308,7 +3308,7 @@
         <v>-0.2262</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.641</v>
+        <v>-0.6605</v>
       </c>
       <c r="E63" t="n">
         <v>-0.5437</v>
@@ -3354,7 +3354,7 @@
         <v>-0.2704</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.6840000000000001</v>
+        <v>-0.7029</v>
       </c>
       <c r="E64" t="n">
         <v>-0.6501</v>
@@ -3400,7 +3400,7 @@
         <v>-0.276</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6894</v>
+        <v>-0.7082000000000001</v>
       </c>
       <c r="E65" t="n">
         <v>-0.6634</v>
@@ -3440,25 +3440,25 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-1.0085</v>
+        <v>-1.0067</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.4195</v>
+        <v>-0.4188</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.8288</v>
+        <v>-0.845</v>
       </c>
       <c r="E66" t="n">
-        <v>-1.0085</v>
+        <v>-1.0067</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.4775</v>
+        <v>-0.4757</v>
       </c>
       <c r="G66" t="n">
         <v>-0.531</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.4775</v>
+        <v>-0.4757</v>
       </c>
       <c r="I66" t="n">
         <v>-0.4797</v>
@@ -3492,7 +3492,7 @@
         <v>-0.4286</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.8376</v>
+        <v>-0.8544</v>
       </c>
       <c r="E67" t="n">
         <v>-1.0303</v>
@@ -3538,7 +3538,7 @@
         <v>-0.5163</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9227</v>
+        <v>-0.9384</v>
       </c>
       <c r="E68" t="n">
         <v>-1.2411</v>
@@ -3578,25 +3578,25 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-1.3548</v>
+        <v>-1.3603</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.5636</v>
+        <v>-0.5659</v>
       </c>
       <c r="D69" t="n">
-        <v>-0.9687</v>
+        <v>-0.9859</v>
       </c>
       <c r="E69" t="n">
-        <v>-1.3548</v>
+        <v>-1.3603</v>
       </c>
       <c r="F69" t="n">
-        <v>1.4839</v>
+        <v>1.4784</v>
       </c>
       <c r="G69" t="n">
         <v>-2.8387</v>
       </c>
       <c r="H69" t="n">
-        <v>1.4839</v>
+        <v>1.4784</v>
       </c>
       <c r="I69" t="n">
         <v>1.4908</v>
@@ -3630,7 +3630,7 @@
         <v>-0.7063</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.1073</v>
+        <v>-1.1204</v>
       </c>
       <c r="E70" t="n">
         <v>-1.6979</v>
@@ -3670,25 +3670,25 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.888</v>
+        <v>-1.8847</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.7854</v>
+        <v>-0.784</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.1841</v>
+        <v>-1.1948</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.888</v>
+        <v>-1.8847</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.888</v>
+        <v>-0.8847</v>
       </c>
       <c r="G71" t="n">
         <v>-1</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.888</v>
+        <v>-0.8847</v>
       </c>
       <c r="I71" t="n">
         <v>-0.8921</v>
@@ -3722,7 +3722,7 @@
         <v>-0.8843</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.2801</v>
+        <v>-1.2907</v>
       </c>
       <c r="E72" t="n">
         <v>-2.1256</v>
@@ -3768,7 +3768,7 @@
         <v>-0.8885999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.2843</v>
+        <v>-1.2949</v>
       </c>
       <c r="E73" t="n">
         <v>-2.1361</v>
@@ -3814,7 +3814,7 @@
         <v>-0.9403</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3344</v>
+        <v>-1.3444</v>
       </c>
       <c r="E74" t="n">
         <v>-2.2602</v>
@@ -3860,7 +3860,7 @@
         <v>-1.0045</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3968</v>
+        <v>-1.4059</v>
       </c>
       <c r="E75" t="n">
         <v>-2.4146</v>
@@ -3906,7 +3906,7 @@
         <v>-1.0845</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4745</v>
+        <v>-1.4825</v>
       </c>
       <c r="E76" t="n">
         <v>-2.607</v>
@@ -3952,7 +3952,7 @@
         <v>-1.1149</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.504</v>
+        <v>-1.5116</v>
       </c>
       <c r="E77" t="n">
         <v>-2.6799</v>
@@ -3998,7 +3998,7 @@
         <v>-1.1265</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5153</v>
+        <v>-1.5228</v>
       </c>
       <c r="E78" t="n">
         <v>-2.708</v>
@@ -4038,25 +4038,25 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-3.2406</v>
+        <v>-3.2271</v>
       </c>
       <c r="C79" t="n">
-        <v>-1.3481</v>
+        <v>-1.3425</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.7305</v>
+        <v>-1.7296</v>
       </c>
       <c r="E79" t="n">
-        <v>-3.2406</v>
+        <v>-3.2271</v>
       </c>
       <c r="F79" t="n">
-        <v>-3.6276</v>
+        <v>-3.6141</v>
       </c>
       <c r="G79" t="n">
         <v>0.387</v>
       </c>
       <c r="H79" t="n">
-        <v>-3.6276</v>
+        <v>-3.6141</v>
       </c>
       <c r="I79" t="n">
         <v>-3.6445</v>
@@ -4090,7 +4090,7 @@
         <v>-2.0702</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.4318</v>
+        <v>-2.4265</v>
       </c>
       <c r="E80" t="n">
         <v>-4.9765</v>
@@ -4136,7 +4136,7 @@
         <v>-2.2662</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.622</v>
+        <v>-2.6142</v>
       </c>
       <c r="E81" t="n">
         <v>-5.4475</v>

--- a/database/event/8064/event_8064_evp_summary.xlsx
+++ b/database/event/8064/event_8064_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.324299999999999</v>
+        <v>8.594900000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>3.4629</v>
+        <v>3.5755</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1652</v>
+        <v>3.2253</v>
       </c>
       <c r="E2" t="n">
-        <v>8.324299999999999</v>
+        <v>8.594900000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2276</v>
+        <v>3.2273</v>
       </c>
       <c r="G2" t="n">
-        <v>5.0967</v>
+        <v>5.109</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3392</v>
+        <v>4.3386</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3392</v>
+        <v>4.3386</v>
       </c>
       <c r="J2" t="n">
-        <v>5.0967</v>
+        <v>5.109</v>
       </c>
       <c r="K2" t="n">
         <v>198</v>
@@ -529,7 +529,7 @@
         <v>229</v>
       </c>
       <c r="M2" t="n">
-        <v>9.4359</v>
+        <v>9.4476</v>
       </c>
       <c r="N2" t="n">
         <v>427</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>8.2273</v>
+        <v>8.351800000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>3.4226</v>
+        <v>3.4744</v>
       </c>
       <c r="D3" t="n">
-        <v>3.121</v>
+        <v>3.1167</v>
       </c>
       <c r="E3" t="n">
-        <v>8.2273</v>
+        <v>8.351800000000001</v>
       </c>
       <c r="F3" t="n">
-        <v>3.114</v>
+        <v>3.1042</v>
       </c>
       <c r="G3" t="n">
-        <v>5.1134</v>
+        <v>5.1139</v>
       </c>
       <c r="H3" t="n">
-        <v>4.0906</v>
+        <v>4.0692</v>
       </c>
       <c r="I3" t="n">
-        <v>4.196</v>
+        <v>4.1741</v>
       </c>
       <c r="J3" t="n">
-        <v>5.1134</v>
+        <v>5.1139</v>
       </c>
       <c r="K3" t="n">
         <v>243</v>
@@ -575,7 +575,7 @@
         <v>239</v>
       </c>
       <c r="M3" t="n">
-        <v>9.3094</v>
+        <v>9.288</v>
       </c>
       <c r="N3" t="n">
         <v>482</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.3825</v>
+        <v>7.5358</v>
       </c>
       <c r="C4" t="n">
-        <v>3.0712</v>
+        <v>3.1349</v>
       </c>
       <c r="D4" t="n">
-        <v>2.7365</v>
+        <v>2.7523</v>
       </c>
       <c r="E4" t="n">
-        <v>7.3825</v>
+        <v>7.5358</v>
       </c>
       <c r="F4" t="n">
-        <v>3.5677</v>
+        <v>3.5675</v>
       </c>
       <c r="G4" t="n">
-        <v>3.8148</v>
+        <v>3.8146</v>
       </c>
       <c r="H4" t="n">
-        <v>5.0836</v>
+        <v>5.0832</v>
       </c>
       <c r="I4" t="n">
-        <v>5.0836</v>
+        <v>5.0832</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8148</v>
+        <v>3.8146</v>
       </c>
       <c r="K4" t="n">
         <v>198</v>
@@ -621,7 +621,7 @@
         <v>229</v>
       </c>
       <c r="M4" t="n">
-        <v>8.898399999999999</v>
+        <v>8.8978</v>
       </c>
       <c r="N4" t="n">
         <v>427</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.1456</v>
+        <v>7.233</v>
       </c>
       <c r="C5" t="n">
-        <v>2.9726</v>
+        <v>3.009</v>
       </c>
       <c r="D5" t="n">
-        <v>2.6286</v>
+        <v>2.617</v>
       </c>
       <c r="E5" t="n">
-        <v>7.1456</v>
+        <v>7.233</v>
       </c>
       <c r="F5" t="n">
-        <v>2.3416</v>
+        <v>2.3414</v>
       </c>
       <c r="G5" t="n">
-        <v>4.804</v>
+        <v>4.8038</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4001</v>
+        <v>2.3996</v>
       </c>
       <c r="I5" t="n">
-        <v>2.4001</v>
+        <v>2.3996</v>
       </c>
       <c r="J5" t="n">
-        <v>4.804</v>
+        <v>4.8038</v>
       </c>
       <c r="K5" t="n">
         <v>198</v>
@@ -667,7 +667,7 @@
         <v>229</v>
       </c>
       <c r="M5" t="n">
-        <v>7.2041</v>
+        <v>7.2034</v>
       </c>
       <c r="N5" t="n">
         <v>427</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.916</v>
+        <v>7.0969</v>
       </c>
       <c r="C6" t="n">
-        <v>2.8771</v>
+        <v>2.9523</v>
       </c>
       <c r="D6" t="n">
-        <v>2.5241</v>
+        <v>2.5562</v>
       </c>
       <c r="E6" t="n">
-        <v>6.916</v>
+        <v>7.0969</v>
       </c>
       <c r="F6" t="n">
-        <v>3.5595</v>
+        <v>3.5594</v>
       </c>
       <c r="G6" t="n">
-        <v>3.3564</v>
+        <v>3.3291</v>
       </c>
       <c r="H6" t="n">
-        <v>5.0658</v>
+        <v>5.0655</v>
       </c>
       <c r="I6" t="n">
-        <v>5.1963</v>
+        <v>5.196</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3564</v>
+        <v>3.3291</v>
       </c>
       <c r="K6" t="n">
         <v>243</v>
@@ -713,7 +713,7 @@
         <v>239</v>
       </c>
       <c r="M6" t="n">
-        <v>8.5527</v>
+        <v>8.5251</v>
       </c>
       <c r="N6" t="n">
         <v>482</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Twistzz</t>
+          <t>NiKo</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>6.4086</v>
+        <v>6.641</v>
       </c>
       <c r="C7" t="n">
-        <v>2.666</v>
+        <v>2.7627</v>
       </c>
       <c r="D7" t="n">
-        <v>2.2931</v>
+        <v>2.3526</v>
       </c>
       <c r="E7" t="n">
-        <v>6.4086</v>
+        <v>6.641</v>
       </c>
       <c r="F7" t="n">
-        <v>4.5321</v>
+        <v>3.3475</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8765</v>
+        <v>3.0047</v>
       </c>
       <c r="H7" t="n">
-        <v>7.1943</v>
+        <v>4.6018</v>
       </c>
       <c r="I7" t="n">
-        <v>7.3797</v>
+        <v>4.6018</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8765</v>
+        <v>3.0047</v>
       </c>
       <c r="K7" t="n">
-        <v>269</v>
+        <v>124</v>
       </c>
       <c r="L7" t="n">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="M7" t="n">
-        <v>9.2562</v>
+        <v>7.6065</v>
       </c>
       <c r="N7" t="n">
-        <v>364</v>
+        <v>212</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NiKo</t>
+          <t>Twistzz</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.3714</v>
+        <v>6.6024</v>
       </c>
       <c r="C8" t="n">
-        <v>2.6505</v>
+        <v>2.7466</v>
       </c>
       <c r="D8" t="n">
-        <v>2.2762</v>
+        <v>2.3353</v>
       </c>
       <c r="E8" t="n">
-        <v>6.3714</v>
+        <v>6.6024</v>
       </c>
       <c r="F8" t="n">
-        <v>3.3473</v>
+        <v>4.538</v>
       </c>
       <c r="G8" t="n">
-        <v>3.0241</v>
+        <v>1.8765</v>
       </c>
       <c r="H8" t="n">
-        <v>4.6013</v>
+        <v>7.2073</v>
       </c>
       <c r="I8" t="n">
-        <v>4.6013</v>
+        <v>7.393</v>
       </c>
       <c r="J8" t="n">
-        <v>3.0241</v>
+        <v>1.8765</v>
       </c>
       <c r="K8" t="n">
-        <v>124</v>
+        <v>269</v>
       </c>
       <c r="L8" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M8" t="n">
-        <v>7.6254</v>
+        <v>9.269500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>212</v>
+        <v>364</v>
       </c>
     </row>
     <row r="9">
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.6261</v>
+        <v>5.9536</v>
       </c>
       <c r="C9" t="n">
-        <v>2.3405</v>
+        <v>2.4767</v>
       </c>
       <c r="D9" t="n">
-        <v>1.9369</v>
+        <v>2.0455</v>
       </c>
       <c r="E9" t="n">
-        <v>5.6261</v>
+        <v>5.9536</v>
       </c>
       <c r="F9" t="n">
-        <v>3.9057</v>
+        <v>3.9055</v>
       </c>
       <c r="G9" t="n">
         <v>1.7204</v>
       </c>
       <c r="H9" t="n">
-        <v>5.8234</v>
+        <v>5.823</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9735</v>
+        <v>5.9731</v>
       </c>
       <c r="J9" t="n">
         <v>1.7204</v>
@@ -851,7 +851,7 @@
         <v>56</v>
       </c>
       <c r="M9" t="n">
-        <v>7.693899999999999</v>
+        <v>7.693499999999999</v>
       </c>
       <c r="N9" t="n">
         <v>308</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>5.3677</v>
+        <v>5.6902</v>
       </c>
       <c r="C10" t="n">
-        <v>2.233</v>
+        <v>2.3671</v>
       </c>
       <c r="D10" t="n">
-        <v>1.8193</v>
+        <v>1.9279</v>
       </c>
       <c r="E10" t="n">
-        <v>5.3677</v>
+        <v>5.6902</v>
       </c>
       <c r="F10" t="n">
-        <v>3.8945</v>
+        <v>3.8947</v>
       </c>
       <c r="G10" t="n">
-        <v>1.4732</v>
+        <v>1.4623</v>
       </c>
       <c r="H10" t="n">
-        <v>5.7989</v>
+        <v>5.7993</v>
       </c>
       <c r="I10" t="n">
-        <v>5.7989</v>
+        <v>5.7993</v>
       </c>
       <c r="J10" t="n">
-        <v>1.4732</v>
+        <v>1.4623</v>
       </c>
       <c r="K10" t="n">
         <v>124</v>
@@ -897,7 +897,7 @@
         <v>88</v>
       </c>
       <c r="M10" t="n">
-        <v>7.2721</v>
+        <v>7.2616</v>
       </c>
       <c r="N10" t="n">
         <v>212</v>
@@ -910,31 +910,31 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5.0741</v>
+        <v>5.3554</v>
       </c>
       <c r="C11" t="n">
-        <v>2.1108</v>
+        <v>2.2279</v>
       </c>
       <c r="D11" t="n">
-        <v>1.6856</v>
+        <v>1.7783</v>
       </c>
       <c r="E11" t="n">
-        <v>5.0741</v>
+        <v>5.3554</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2963</v>
+        <v>4.2908</v>
       </c>
       <c r="G11" t="n">
-        <v>0.7778</v>
+        <v>0.7774</v>
       </c>
       <c r="H11" t="n">
-        <v>6.6783</v>
+        <v>6.6663</v>
       </c>
       <c r="I11" t="n">
-        <v>6.6783</v>
+        <v>6.6663</v>
       </c>
       <c r="J11" t="n">
-        <v>0.7778</v>
+        <v>0.7774</v>
       </c>
       <c r="K11" t="n">
         <v>185</v>
@@ -943,7 +943,7 @@
         <v>66</v>
       </c>
       <c r="M11" t="n">
-        <v>7.4561</v>
+        <v>7.4437</v>
       </c>
       <c r="N11" t="n">
         <v>251</v>
@@ -956,28 +956,28 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>4.1393</v>
+        <v>4.0851</v>
       </c>
       <c r="C12" t="n">
-        <v>1.722</v>
+        <v>1.6994</v>
       </c>
       <c r="D12" t="n">
-        <v>1.2601</v>
+        <v>1.2109</v>
       </c>
       <c r="E12" t="n">
-        <v>4.1393</v>
+        <v>4.0851</v>
       </c>
       <c r="F12" t="n">
-        <v>1.6056</v>
+        <v>1.6053</v>
       </c>
       <c r="G12" t="n">
         <v>2.5337</v>
       </c>
       <c r="H12" t="n">
-        <v>1.6056</v>
+        <v>1.6053</v>
       </c>
       <c r="I12" t="n">
-        <v>1.647</v>
+        <v>1.6467</v>
       </c>
       <c r="J12" t="n">
         <v>2.5337</v>
@@ -989,7 +989,7 @@
         <v>95</v>
       </c>
       <c r="M12" t="n">
-        <v>4.1807</v>
+        <v>4.180400000000001</v>
       </c>
       <c r="N12" t="n">
         <v>364</v>
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>4.1194</v>
+        <v>4.0646</v>
       </c>
       <c r="C13" t="n">
-        <v>1.7137</v>
+        <v>1.6909</v>
       </c>
       <c r="D13" t="n">
-        <v>1.251</v>
+        <v>1.2017</v>
       </c>
       <c r="E13" t="n">
-        <v>4.1194</v>
+        <v>4.0646</v>
       </c>
       <c r="F13" t="n">
-        <v>3.372</v>
+        <v>3.3721</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7474</v>
+        <v>0.7385</v>
       </c>
       <c r="H13" t="n">
-        <v>4.6553</v>
+        <v>4.6555</v>
       </c>
       <c r="I13" t="n">
-        <v>4.6553</v>
+        <v>4.6555</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7474</v>
+        <v>0.7385</v>
       </c>
       <c r="K13" t="n">
         <v>124</v>
@@ -1035,7 +1035,7 @@
         <v>88</v>
       </c>
       <c r="M13" t="n">
-        <v>5.4027</v>
+        <v>5.394</v>
       </c>
       <c r="N13" t="n">
         <v>212</v>
@@ -1048,31 +1048,31 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.9361</v>
+        <v>4.0153</v>
       </c>
       <c r="C14" t="n">
-        <v>1.6374</v>
+        <v>1.6704</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1676</v>
+        <v>1.1797</v>
       </c>
       <c r="E14" t="n">
-        <v>3.9361</v>
+        <v>4.0153</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4231</v>
+        <v>3.4328</v>
       </c>
       <c r="G14" t="n">
-        <v>0.513</v>
+        <v>0.5131</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7671</v>
+        <v>4.7883</v>
       </c>
       <c r="I14" t="n">
-        <v>4.7671</v>
+        <v>4.7883</v>
       </c>
       <c r="J14" t="n">
-        <v>0.513</v>
+        <v>0.5131</v>
       </c>
       <c r="K14" t="n">
         <v>286</v>
@@ -1081,7 +1081,7 @@
         <v>36</v>
       </c>
       <c r="M14" t="n">
-        <v>5.2801</v>
+        <v>5.301399999999999</v>
       </c>
       <c r="N14" t="n">
         <v>322</v>
@@ -1094,16 +1094,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.7644</v>
+        <v>3.8778</v>
       </c>
       <c r="C15" t="n">
-        <v>1.566</v>
+        <v>1.6132</v>
       </c>
       <c r="D15" t="n">
-        <v>1.0894</v>
+        <v>1.1183</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7644</v>
+        <v>3.8778</v>
       </c>
       <c r="F15" t="n">
         <v>2.4969</v>
@@ -1136,415 +1136,415 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SunPayus</t>
+          <t>XANTARES</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3.7448</v>
+        <v>3.8235</v>
       </c>
       <c r="C16" t="n">
-        <v>1.5579</v>
+        <v>1.5906</v>
       </c>
       <c r="D16" t="n">
-        <v>1.0805</v>
+        <v>1.0941</v>
       </c>
       <c r="E16" t="n">
-        <v>3.7448</v>
+        <v>3.8235</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2601</v>
+        <v>3.8177</v>
       </c>
       <c r="G16" t="n">
-        <v>0.4847</v>
+        <v>-0.3617</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4105</v>
+        <v>5.6309</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4105</v>
+        <v>5.6309</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4847</v>
+        <v>-0.3617</v>
       </c>
       <c r="K16" t="n">
-        <v>185</v>
+        <v>162</v>
       </c>
       <c r="L16" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="M16" t="n">
-        <v>4.8952</v>
+        <v>5.2692</v>
       </c>
       <c r="N16" t="n">
-        <v>251</v>
+        <v>205</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>kyxsan</t>
+          <t>SunPayus</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3.5418</v>
+        <v>3.7974</v>
       </c>
       <c r="C17" t="n">
-        <v>1.4734</v>
+        <v>1.5797</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9881</v>
+        <v>1.0824</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5418</v>
+        <v>3.7974</v>
       </c>
       <c r="F17" t="n">
-        <v>1.8347</v>
+        <v>3.2602</v>
       </c>
       <c r="G17" t="n">
-        <v>1.7071</v>
+        <v>0.4959</v>
       </c>
       <c r="H17" t="n">
-        <v>1.8347</v>
+        <v>4.4107</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8347</v>
+        <v>4.4107</v>
       </c>
       <c r="J17" t="n">
-        <v>1.7071</v>
+        <v>0.4959</v>
       </c>
       <c r="K17" t="n">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="L17" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.5418</v>
+        <v>4.9066</v>
       </c>
       <c r="N17" t="n">
-        <v>212</v>
+        <v>251</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>HeavyGod</t>
+          <t>Moseyuh</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>3.5146</v>
+        <v>3.5367</v>
       </c>
       <c r="C18" t="n">
-        <v>1.4621</v>
+        <v>1.4713</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9757</v>
+        <v>0.9659</v>
       </c>
       <c r="E18" t="n">
-        <v>3.5146</v>
+        <v>3.5367</v>
       </c>
       <c r="F18" t="n">
-        <v>3.5152</v>
+        <v>3.2215</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>4.9687</v>
+        <v>4.3259</v>
       </c>
       <c r="I18" t="n">
-        <v>4.9687</v>
+        <v>4.3259</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>185</v>
+        <v>212</v>
       </c>
       <c r="L18" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>4.9681</v>
+        <v>4.3259</v>
       </c>
       <c r="N18" t="n">
-        <v>251</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>XANTARES</t>
+          <t>m0NESY</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>3.456</v>
+        <v>3.5028</v>
       </c>
       <c r="C19" t="n">
-        <v>1.4377</v>
+        <v>1.4572</v>
       </c>
       <c r="D19" t="n">
-        <v>0.949</v>
+        <v>0.9508</v>
       </c>
       <c r="E19" t="n">
-        <v>3.456</v>
+        <v>3.5028</v>
       </c>
       <c r="F19" t="n">
-        <v>3.8177</v>
+        <v>3.2861</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3617</v>
+        <v>0.1117</v>
       </c>
       <c r="H19" t="n">
-        <v>5.6309</v>
+        <v>4.4674</v>
       </c>
       <c r="I19" t="n">
-        <v>5.6309</v>
+        <v>4.4674</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.3617</v>
+        <v>0.1117</v>
       </c>
       <c r="K19" t="n">
-        <v>162</v>
+        <v>124</v>
       </c>
       <c r="L19" t="n">
-        <v>43</v>
+        <v>88</v>
       </c>
       <c r="M19" t="n">
-        <v>5.2692</v>
+        <v>4.5791</v>
       </c>
       <c r="N19" t="n">
-        <v>205</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>m0NESY</t>
+          <t>HeavyGod</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3.3966</v>
+        <v>3.4636</v>
       </c>
       <c r="C20" t="n">
-        <v>1.413</v>
+        <v>1.4409</v>
       </c>
       <c r="D20" t="n">
-        <v>0.922</v>
+        <v>0.9333</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3966</v>
+        <v>3.4636</v>
       </c>
       <c r="F20" t="n">
-        <v>3.286</v>
+        <v>3.5151</v>
       </c>
       <c r="G20" t="n">
-        <v>0.1106</v>
+        <v>-0.0008</v>
       </c>
       <c r="H20" t="n">
-        <v>4.4671</v>
+        <v>4.9686</v>
       </c>
       <c r="I20" t="n">
-        <v>4.4671</v>
+        <v>4.9686</v>
       </c>
       <c r="J20" t="n">
-        <v>0.1106</v>
+        <v>-0.0008</v>
       </c>
       <c r="K20" t="n">
-        <v>124</v>
+        <v>185</v>
       </c>
       <c r="L20" t="n">
-        <v>88</v>
+        <v>66</v>
       </c>
       <c r="M20" t="n">
-        <v>4.5777</v>
+        <v>4.9678</v>
       </c>
       <c r="N20" t="n">
-        <v>212</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ultimate</t>
+          <t>nqz</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3.3798</v>
+        <v>3.4117</v>
       </c>
       <c r="C21" t="n">
-        <v>1.406</v>
+        <v>1.4193</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9144</v>
+        <v>0.9101</v>
       </c>
       <c r="E21" t="n">
-        <v>3.3798</v>
+        <v>3.4117</v>
       </c>
       <c r="F21" t="n">
-        <v>3.265</v>
+        <v>3.2936</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1148</v>
+        <v>0.0324</v>
       </c>
       <c r="H21" t="n">
-        <v>4.4212</v>
+        <v>4.4838</v>
       </c>
       <c r="I21" t="n">
-        <v>4.5351</v>
+        <v>4.4838</v>
       </c>
       <c r="J21" t="n">
-        <v>0.1148</v>
+        <v>0.0324</v>
       </c>
       <c r="K21" t="n">
-        <v>269</v>
+        <v>286</v>
       </c>
       <c r="L21" t="n">
-        <v>95</v>
+        <v>36</v>
       </c>
       <c r="M21" t="n">
-        <v>4.6499</v>
+        <v>4.5162</v>
       </c>
       <c r="N21" t="n">
-        <v>364</v>
+        <v>322</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nqz</t>
+          <t>ultimate</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>3.3314</v>
+        <v>3.3942</v>
       </c>
       <c r="C22" t="n">
-        <v>1.3859</v>
+        <v>1.412</v>
       </c>
       <c r="D22" t="n">
-        <v>0.8923</v>
+        <v>0.9023</v>
       </c>
       <c r="E22" t="n">
-        <v>3.3314</v>
+        <v>3.3942</v>
       </c>
       <c r="F22" t="n">
-        <v>3.2995</v>
+        <v>3.2649</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0319</v>
+        <v>0.1148</v>
       </c>
       <c r="H22" t="n">
-        <v>4.4966</v>
+        <v>4.421</v>
       </c>
       <c r="I22" t="n">
-        <v>4.4966</v>
+        <v>4.5349</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0319</v>
+        <v>0.1148</v>
       </c>
       <c r="K22" t="n">
-        <v>286</v>
+        <v>269</v>
       </c>
       <c r="L22" t="n">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="M22" t="n">
-        <v>4.5285</v>
+        <v>4.6497</v>
       </c>
       <c r="N22" t="n">
-        <v>322</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>910</t>
+          <t>kyxsan</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>3.2277</v>
+        <v>3.3587</v>
       </c>
       <c r="C23" t="n">
-        <v>1.3427</v>
+        <v>1.3972</v>
       </c>
       <c r="D23" t="n">
-        <v>0.8451</v>
+        <v>0.8864</v>
       </c>
       <c r="E23" t="n">
-        <v>3.2277</v>
+        <v>3.3587</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8784</v>
+        <v>1.8032</v>
       </c>
       <c r="G23" t="n">
-        <v>2.3493</v>
+        <v>1.7078</v>
       </c>
       <c r="H23" t="n">
-        <v>0.8784</v>
+        <v>1.8032</v>
       </c>
       <c r="I23" t="n">
-        <v>0.901</v>
+        <v>1.8032</v>
       </c>
       <c r="J23" t="n">
-        <v>2.3493</v>
+        <v>1.7078</v>
       </c>
       <c r="K23" t="n">
-        <v>243</v>
+        <v>124</v>
       </c>
       <c r="L23" t="n">
-        <v>239</v>
+        <v>88</v>
       </c>
       <c r="M23" t="n">
-        <v>3.2503</v>
+        <v>3.511</v>
       </c>
       <c r="N23" t="n">
-        <v>482</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Moseyuh</t>
+          <t>jcobbb</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3.2215</v>
+        <v>3.2705</v>
       </c>
       <c r="C24" t="n">
-        <v>1.3402</v>
+        <v>1.3605</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8423</v>
+        <v>0.847</v>
       </c>
       <c r="E24" t="n">
-        <v>3.2215</v>
+        <v>3.2705</v>
       </c>
       <c r="F24" t="n">
-        <v>3.2215</v>
+        <v>3.0667</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>4.326</v>
+        <v>3.9871</v>
       </c>
       <c r="I24" t="n">
-        <v>4.326</v>
+        <v>3.9871</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>212</v>
+        <v>256</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>4.326</v>
+        <v>3.9871</v>
       </c>
       <c r="N24" t="n">
-        <v>212</v>
+        <v>256</v>
       </c>
     </row>
     <row r="25">
@@ -1554,28 +1554,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3.1189</v>
+        <v>3.2143</v>
       </c>
       <c r="C25" t="n">
-        <v>1.2975</v>
+        <v>1.3372</v>
       </c>
       <c r="D25" t="n">
-        <v>0.7956</v>
+        <v>0.8219</v>
       </c>
       <c r="E25" t="n">
-        <v>3.1189</v>
+        <v>3.2143</v>
       </c>
       <c r="F25" t="n">
-        <v>3.1451</v>
+        <v>3.1448</v>
       </c>
       <c r="G25" t="n">
         <v>-0.0262</v>
       </c>
       <c r="H25" t="n">
-        <v>4.1586</v>
+        <v>4.1581</v>
       </c>
       <c r="I25" t="n">
-        <v>4.2658</v>
+        <v>4.2653</v>
       </c>
       <c r="J25" t="n">
         <v>-0.0262</v>
@@ -1587,7 +1587,7 @@
         <v>56</v>
       </c>
       <c r="M25" t="n">
-        <v>4.239599999999999</v>
+        <v>4.2391</v>
       </c>
       <c r="N25" t="n">
         <v>308</v>
@@ -1596,415 +1596,415 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>frozen</t>
+          <t>910</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.1018</v>
+        <v>3.2058</v>
       </c>
       <c r="C26" t="n">
-        <v>1.2904</v>
+        <v>1.3336</v>
       </c>
       <c r="D26" t="n">
-        <v>0.7877999999999999</v>
+        <v>0.8181</v>
       </c>
       <c r="E26" t="n">
-        <v>3.1018</v>
+        <v>3.2058</v>
       </c>
       <c r="F26" t="n">
-        <v>3.1018</v>
+        <v>0.8994</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>2.3432</v>
       </c>
       <c r="H26" t="n">
-        <v>4.064</v>
+        <v>0.8994</v>
       </c>
       <c r="I26" t="n">
-        <v>4.064</v>
+        <v>0.9226</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>2.3432</v>
       </c>
       <c r="K26" t="n">
-        <v>256</v>
+        <v>243</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="M26" t="n">
-        <v>4.064</v>
+        <v>3.2658</v>
       </c>
       <c r="N26" t="n">
-        <v>256</v>
+        <v>482</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>jcobbb</t>
+          <t>fame</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.0608</v>
+        <v>3.1834</v>
       </c>
       <c r="C27" t="n">
-        <v>1.2733</v>
+        <v>1.3243</v>
       </c>
       <c r="D27" t="n">
-        <v>0.7691</v>
+        <v>0.8081</v>
       </c>
       <c r="E27" t="n">
-        <v>3.0608</v>
+        <v>3.1834</v>
       </c>
       <c r="F27" t="n">
-        <v>3.0608</v>
+        <v>2.877</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>3.9743</v>
+        <v>3.5719</v>
       </c>
       <c r="I27" t="n">
-        <v>3.9743</v>
+        <v>3.5719</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9743</v>
+        <v>3.5719</v>
       </c>
       <c r="N27" t="n">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Wicadia</t>
+          <t>frozen</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2.9158</v>
+        <v>3.1413</v>
       </c>
       <c r="C28" t="n">
-        <v>1.213</v>
+        <v>1.3068</v>
       </c>
       <c r="D28" t="n">
-        <v>0.7030999999999999</v>
+        <v>0.7893</v>
       </c>
       <c r="E28" t="n">
-        <v>2.9158</v>
+        <v>3.1413</v>
       </c>
       <c r="F28" t="n">
-        <v>3.3243</v>
+        <v>3.1057</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>4.551</v>
+        <v>4.0725</v>
       </c>
       <c r="I28" t="n">
-        <v>4.551</v>
+        <v>4.0725</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4085</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>162</v>
+        <v>256</v>
       </c>
       <c r="L28" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1425</v>
+        <v>4.0725</v>
       </c>
       <c r="N28" t="n">
-        <v>205</v>
+        <v>256</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>fame</t>
+          <t>nilo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>2.8711</v>
+        <v>3.0372</v>
       </c>
       <c r="C29" t="n">
-        <v>1.1944</v>
+        <v>1.2635</v>
       </c>
       <c r="D29" t="n">
-        <v>0.6828</v>
+        <v>0.7428</v>
       </c>
       <c r="E29" t="n">
-        <v>2.8711</v>
+        <v>3.0372</v>
       </c>
       <c r="F29" t="n">
-        <v>2.8711</v>
+        <v>2.8539</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>3.5589</v>
+        <v>3.5213</v>
       </c>
       <c r="I29" t="n">
-        <v>3.5589</v>
+        <v>3.5213</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>3.5589</v>
+        <v>3.5213</v>
       </c>
       <c r="N29" t="n">
-        <v>262</v>
+        <v>223</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>nilo</t>
+          <t>Wicadia</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>2.8463</v>
+        <v>3.0364</v>
       </c>
       <c r="C30" t="n">
-        <v>1.1841</v>
+        <v>1.2632</v>
       </c>
       <c r="D30" t="n">
-        <v>0.6715</v>
+        <v>0.7425</v>
       </c>
       <c r="E30" t="n">
-        <v>2.8463</v>
+        <v>3.0364</v>
       </c>
       <c r="F30" t="n">
-        <v>2.8463</v>
+        <v>3.3243</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="H30" t="n">
-        <v>3.5048</v>
+        <v>4.551</v>
       </c>
       <c r="I30" t="n">
-        <v>3.5048</v>
+        <v>4.551</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>-0.4085</v>
       </c>
       <c r="K30" t="n">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5048</v>
+        <v>4.1425</v>
       </c>
       <c r="N30" t="n">
-        <v>223</v>
+        <v>205</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bLitz</t>
+          <t>rain</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2.8292</v>
+        <v>3.0109</v>
       </c>
       <c r="C31" t="n">
-        <v>1.177</v>
+        <v>1.2525</v>
       </c>
       <c r="D31" t="n">
-        <v>0.6637</v>
+        <v>0.7311</v>
       </c>
       <c r="E31" t="n">
-        <v>2.8292</v>
+        <v>3.0109</v>
       </c>
       <c r="F31" t="n">
-        <v>1.2179</v>
+        <v>2.7984</v>
       </c>
       <c r="G31" t="n">
-        <v>1.6113</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>1.2179</v>
+        <v>3.3999</v>
       </c>
       <c r="I31" t="n">
-        <v>1.2493</v>
+        <v>3.3999</v>
       </c>
       <c r="J31" t="n">
-        <v>1.6113</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="L31" t="n">
-        <v>239</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>2.8606</v>
+        <v>3.3999</v>
       </c>
       <c r="N31" t="n">
-        <v>482</v>
+        <v>256</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>rain</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2.8071</v>
+        <v>2.7903</v>
       </c>
       <c r="C32" t="n">
-        <v>1.1678</v>
+        <v>1.1608</v>
       </c>
       <c r="D32" t="n">
-        <v>0.6536</v>
+        <v>0.6325</v>
       </c>
       <c r="E32" t="n">
-        <v>2.8071</v>
+        <v>2.7903</v>
       </c>
       <c r="F32" t="n">
-        <v>2.8071</v>
+        <v>2.6833</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>3.4189</v>
+        <v>3.148</v>
       </c>
       <c r="I32" t="n">
-        <v>3.4189</v>
+        <v>3.148</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4189</v>
+        <v>3.148</v>
       </c>
       <c r="N32" t="n">
-        <v>256</v>
+        <v>242</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JamYoung</t>
+          <t>bLitz</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>2.6982</v>
+        <v>2.6592</v>
       </c>
       <c r="C33" t="n">
-        <v>1.1225</v>
+        <v>1.1062</v>
       </c>
       <c r="D33" t="n">
-        <v>0.6041</v>
+        <v>0.574</v>
       </c>
       <c r="E33" t="n">
-        <v>2.6982</v>
+        <v>2.6592</v>
       </c>
       <c r="F33" t="n">
-        <v>2.6982</v>
+        <v>1.2179</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>1.6126</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1806</v>
+        <v>1.2179</v>
       </c>
       <c r="I33" t="n">
-        <v>3.1806</v>
+        <v>1.2493</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>1.6126</v>
       </c>
       <c r="K33" t="n">
-        <v>212</v>
+        <v>243</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>239</v>
       </c>
       <c r="M33" t="n">
-        <v>3.1806</v>
+        <v>2.8619</v>
       </c>
       <c r="N33" t="n">
-        <v>212</v>
+        <v>482</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>JamYoung</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>2.6886</v>
+        <v>2.6285</v>
       </c>
       <c r="C34" t="n">
-        <v>1.1185</v>
+        <v>1.0935</v>
       </c>
       <c r="D34" t="n">
-        <v>0.5997</v>
+        <v>0.5603</v>
       </c>
       <c r="E34" t="n">
-        <v>2.6886</v>
+        <v>2.6285</v>
       </c>
       <c r="F34" t="n">
-        <v>2.6886</v>
+        <v>2.692</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>3.1596</v>
+        <v>3.167</v>
       </c>
       <c r="I34" t="n">
-        <v>3.1596</v>
+        <v>3.167</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>242</v>
+        <v>212</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>3.1596</v>
+        <v>3.167</v>
       </c>
       <c r="N34" t="n">
-        <v>242</v>
+        <v>212</v>
       </c>
     </row>
     <row r="35">
@@ -2014,31 +2014,31 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>2.5902</v>
+        <v>2.554</v>
       </c>
       <c r="C35" t="n">
-        <v>1.0775</v>
+        <v>1.0625</v>
       </c>
       <c r="D35" t="n">
-        <v>0.5548999999999999</v>
+        <v>0.527</v>
       </c>
       <c r="E35" t="n">
-        <v>2.5902</v>
+        <v>2.554</v>
       </c>
       <c r="F35" t="n">
-        <v>2.5494</v>
+        <v>2.544</v>
       </c>
       <c r="G35" t="n">
-        <v>0.0408</v>
+        <v>0.0414</v>
       </c>
       <c r="H35" t="n">
-        <v>2.8548</v>
+        <v>2.8431</v>
       </c>
       <c r="I35" t="n">
-        <v>2.8548</v>
+        <v>2.8431</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0408</v>
+        <v>0.0414</v>
       </c>
       <c r="K35" t="n">
         <v>286</v>
@@ -2047,7 +2047,7 @@
         <v>36</v>
       </c>
       <c r="M35" t="n">
-        <v>2.8956</v>
+        <v>2.8845</v>
       </c>
       <c r="N35" t="n">
         <v>322</v>
@@ -2056,139 +2056,139 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>latto</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2.1297</v>
+        <v>2.3083</v>
       </c>
       <c r="C36" t="n">
-        <v>0.886</v>
+        <v>0.9603</v>
       </c>
       <c r="D36" t="n">
-        <v>0.3453</v>
+        <v>0.4172</v>
       </c>
       <c r="E36" t="n">
-        <v>2.1297</v>
+        <v>2.3083</v>
       </c>
       <c r="F36" t="n">
-        <v>2.1297</v>
+        <v>1.9456</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>2.1297</v>
+        <v>1.9456</v>
       </c>
       <c r="I36" t="n">
-        <v>2.1297</v>
+        <v>1.9456</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>2.1297</v>
+        <v>1.9456</v>
       </c>
       <c r="N36" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>yuurih</t>
+          <t>xfl0ud</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2.1006</v>
+        <v>2.2355</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8739</v>
+        <v>0.93</v>
       </c>
       <c r="D37" t="n">
-        <v>0.332</v>
+        <v>0.3847</v>
       </c>
       <c r="E37" t="n">
-        <v>2.1006</v>
+        <v>2.2355</v>
       </c>
       <c r="F37" t="n">
-        <v>0.2089</v>
+        <v>2.0233</v>
       </c>
       <c r="G37" t="n">
-        <v>1.8917</v>
+        <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0.2089</v>
+        <v>2.0233</v>
       </c>
       <c r="I37" t="n">
-        <v>0.2089</v>
+        <v>2.0233</v>
       </c>
       <c r="J37" t="n">
-        <v>1.8917</v>
+        <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="L37" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>2.1006</v>
+        <v>2.0233</v>
       </c>
       <c r="N37" t="n">
-        <v>427</v>
+        <v>223</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>xfl0ud</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2.0344</v>
+        <v>2.1897</v>
       </c>
       <c r="C38" t="n">
-        <v>0.8463000000000001</v>
+        <v>0.9109</v>
       </c>
       <c r="D38" t="n">
-        <v>0.3019</v>
+        <v>0.3643</v>
       </c>
       <c r="E38" t="n">
-        <v>2.0344</v>
+        <v>2.1897</v>
       </c>
       <c r="F38" t="n">
-        <v>2.0344</v>
+        <v>2.1422</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>2.0344</v>
+        <v>2.1422</v>
       </c>
       <c r="I38" t="n">
-        <v>2.0344</v>
+        <v>2.1422</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>2.0344</v>
+        <v>2.1422</v>
       </c>
       <c r="N38" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39">
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2.0042</v>
+        <v>2.0855</v>
       </c>
       <c r="C39" t="n">
-        <v>0.8338</v>
+        <v>0.8676</v>
       </c>
       <c r="D39" t="n">
-        <v>0.2881</v>
+        <v>0.3177</v>
       </c>
       <c r="E39" t="n">
-        <v>2.0042</v>
+        <v>2.0855</v>
       </c>
       <c r="F39" t="n">
-        <v>2.0042</v>
+        <v>2.0039</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>2.0042</v>
+        <v>2.0039</v>
       </c>
       <c r="I39" t="n">
-        <v>2.0042</v>
+        <v>2.0039</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>2.0042</v>
+        <v>2.0039</v>
       </c>
       <c r="N39" t="n">
         <v>262</v>
@@ -2240,323 +2240,323 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>latto</t>
+          <t>Maka</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1.9311</v>
+        <v>1.9446</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8033</v>
+        <v>0.8090000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2549</v>
+        <v>0.2548</v>
       </c>
       <c r="E40" t="n">
-        <v>1.9311</v>
+        <v>1.9446</v>
       </c>
       <c r="F40" t="n">
-        <v>1.9311</v>
+        <v>1.8822</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>1.9311</v>
+        <v>1.8822</v>
       </c>
       <c r="I40" t="n">
-        <v>1.9311</v>
+        <v>1.8822</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="L40" t="n">
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>1.9311</v>
+        <v>1.8822</v>
       </c>
       <c r="N40" t="n">
-        <v>198</v>
+        <v>262</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Maka</t>
+          <t>yuurih</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1.8824</v>
+        <v>1.9387</v>
       </c>
       <c r="C41" t="n">
-        <v>0.7831</v>
+        <v>0.8065</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2327</v>
+        <v>0.2522</v>
       </c>
       <c r="E41" t="n">
-        <v>1.8824</v>
+        <v>1.9387</v>
       </c>
       <c r="F41" t="n">
-        <v>1.8824</v>
+        <v>0.2349</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>1.8913</v>
       </c>
       <c r="H41" t="n">
-        <v>1.8824</v>
+        <v>0.2349</v>
       </c>
       <c r="I41" t="n">
-        <v>1.8824</v>
+        <v>0.2349</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>1.8913</v>
       </c>
       <c r="K41" t="n">
-        <v>262</v>
+        <v>198</v>
       </c>
       <c r="L41" t="n">
-        <v>0</v>
+        <v>229</v>
       </c>
       <c r="M41" t="n">
-        <v>1.8824</v>
+        <v>2.1262</v>
       </c>
       <c r="N41" t="n">
-        <v>262</v>
+        <v>427</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>huNter-</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>1.838</v>
+        <v>1.8672</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7645999999999999</v>
+        <v>0.7768</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2125</v>
+        <v>0.2202</v>
       </c>
       <c r="E42" t="n">
-        <v>1.838</v>
+        <v>1.8672</v>
       </c>
       <c r="F42" t="n">
-        <v>1.4226</v>
+        <v>1.7862</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4154</v>
+        <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>1.4226</v>
+        <v>1.7862</v>
       </c>
       <c r="I42" t="n">
-        <v>1.4226</v>
+        <v>1.7862</v>
       </c>
       <c r="J42" t="n">
-        <v>0.4154</v>
+        <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="L42" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>1.838</v>
+        <v>1.7862</v>
       </c>
       <c r="N42" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>Starry</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1.7637</v>
+        <v>1.7798</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7337</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1787</v>
+        <v>0.1812</v>
       </c>
       <c r="E43" t="n">
-        <v>1.7637</v>
+        <v>1.7798</v>
       </c>
       <c r="F43" t="n">
-        <v>1.7637</v>
+        <v>1.6991</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>1.7637</v>
+        <v>1.6991</v>
       </c>
       <c r="I43" t="n">
-        <v>1.7637</v>
+        <v>1.6991</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>1.7637</v>
+        <v>1.6991</v>
       </c>
       <c r="N43" t="n">
-        <v>242</v>
+        <v>146</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>tO0RO</t>
+          <t>huNter-</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1.7309</v>
+        <v>1.702</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7201</v>
+        <v>0.708</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1637</v>
+        <v>0.1464</v>
       </c>
       <c r="E44" t="n">
-        <v>1.7309</v>
+        <v>1.702</v>
       </c>
       <c r="F44" t="n">
-        <v>1.7309</v>
+        <v>1.4226</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>0.4153</v>
       </c>
       <c r="H44" t="n">
-        <v>1.7309</v>
+        <v>1.4226</v>
       </c>
       <c r="I44" t="n">
-        <v>1.7309</v>
+        <v>1.4226</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>0.4153</v>
       </c>
       <c r="K44" t="n">
-        <v>262</v>
+        <v>185</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M44" t="n">
-        <v>1.7309</v>
+        <v>1.8379</v>
       </c>
       <c r="N44" t="n">
-        <v>262</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Starry</t>
+          <t>tO0RO</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1.7129</v>
+        <v>1.6931</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7126</v>
+        <v>0.7043</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1555</v>
+        <v>0.1425</v>
       </c>
       <c r="E45" t="n">
-        <v>1.7129</v>
+        <v>1.6931</v>
       </c>
       <c r="F45" t="n">
-        <v>1.7129</v>
+        <v>1.7305</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>1.7129</v>
+        <v>1.7305</v>
       </c>
       <c r="I45" t="n">
-        <v>1.7129</v>
+        <v>1.7305</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>146</v>
+        <v>262</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>1.7129</v>
+        <v>1.7305</v>
       </c>
       <c r="N45" t="n">
-        <v>146</v>
+        <v>262</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NertZ</t>
+          <t>FL1T</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>1.4932</v>
+        <v>1.6201</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6212</v>
+        <v>0.674</v>
       </c>
       <c r="D46" t="n">
-        <v>0.0555</v>
+        <v>0.1098</v>
       </c>
       <c r="E46" t="n">
-        <v>1.4932</v>
+        <v>1.6201</v>
       </c>
       <c r="F46" t="n">
-        <v>2.6023</v>
+        <v>1.4752</v>
       </c>
       <c r="G46" t="n">
-        <v>-1.1091</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>2.9707</v>
+        <v>1.4752</v>
       </c>
       <c r="I46" t="n">
-        <v>3.0473</v>
+        <v>1.4752</v>
       </c>
       <c r="J46" t="n">
-        <v>-1.1091</v>
+        <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="L46" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1.9382</v>
+        <v>1.4752</v>
       </c>
       <c r="N46" t="n">
-        <v>364</v>
+        <v>262</v>
       </c>
     </row>
     <row r="47">
@@ -2566,28 +2566,28 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1.4831</v>
+        <v>1.5392</v>
       </c>
       <c r="C47" t="n">
-        <v>0.617</v>
+        <v>0.6403</v>
       </c>
       <c r="D47" t="n">
-        <v>0.0509</v>
+        <v>0.0737</v>
       </c>
       <c r="E47" t="n">
-        <v>1.4831</v>
+        <v>1.5392</v>
       </c>
       <c r="F47" t="n">
-        <v>1.4831</v>
+        <v>1.4827</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>1.4831</v>
+        <v>1.4827</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4831</v>
+        <v>1.4827</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -2599,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>1.4831</v>
+        <v>1.4827</v>
       </c>
       <c r="N47" t="n">
         <v>242</v>
@@ -2608,185 +2608,185 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>FL1T</t>
+          <t>Jee</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1.4457</v>
+        <v>1.5168</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6014</v>
+        <v>0.631</v>
       </c>
       <c r="D48" t="n">
-        <v>0.0339</v>
+        <v>0.06370000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>1.4457</v>
+        <v>1.5168</v>
       </c>
       <c r="F48" t="n">
-        <v>1.4457</v>
+        <v>1.4285</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>1.4457</v>
+        <v>1.4285</v>
       </c>
       <c r="I48" t="n">
-        <v>1.4457</v>
+        <v>1.4285</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="L48" t="n">
         <v>0</v>
       </c>
       <c r="M48" t="n">
-        <v>1.4457</v>
+        <v>1.4285</v>
       </c>
       <c r="N48" t="n">
-        <v>262</v>
+        <v>212</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Jee</t>
+          <t>NertZ</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1.4285</v>
+        <v>1.4709</v>
       </c>
       <c r="C49" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.6119</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0261</v>
+        <v>0.0432</v>
       </c>
       <c r="E49" t="n">
-        <v>1.4285</v>
+        <v>1.4709</v>
       </c>
       <c r="F49" t="n">
-        <v>1.4285</v>
+        <v>2.6021</v>
       </c>
       <c r="G49" t="n">
-        <v>0</v>
+        <v>-1.1091</v>
       </c>
       <c r="H49" t="n">
-        <v>1.4285</v>
+        <v>2.9704</v>
       </c>
       <c r="I49" t="n">
-        <v>1.4285</v>
+        <v>3.0469</v>
       </c>
       <c r="J49" t="n">
-        <v>0</v>
+        <v>-1.1091</v>
       </c>
       <c r="K49" t="n">
-        <v>212</v>
+        <v>269</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="M49" t="n">
-        <v>1.4285</v>
+        <v>1.9378</v>
       </c>
       <c r="N49" t="n">
-        <v>212</v>
+        <v>364</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>jabbi</t>
+          <t>n1ssim</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1.426</v>
+        <v>1.3984</v>
       </c>
       <c r="C50" t="n">
-        <v>0.5931999999999999</v>
+        <v>0.5817</v>
       </c>
       <c r="D50" t="n">
-        <v>0.0249</v>
+        <v>0.0108</v>
       </c>
       <c r="E50" t="n">
-        <v>1.426</v>
+        <v>1.3984</v>
       </c>
       <c r="F50" t="n">
-        <v>2.0569</v>
+        <v>1.3754</v>
       </c>
       <c r="G50" t="n">
-        <v>-0.6309</v>
+        <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>2.0569</v>
+        <v>1.3754</v>
       </c>
       <c r="I50" t="n">
-        <v>2.1099</v>
+        <v>1.3754</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.6309</v>
+        <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>252</v>
+        <v>198</v>
       </c>
       <c r="L50" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M50" t="n">
-        <v>1.479</v>
+        <v>1.3754</v>
       </c>
       <c r="N50" t="n">
-        <v>308</v>
+        <v>198</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>n1ssim</t>
+          <t>jabbi</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>1.3538</v>
+        <v>1.3805</v>
       </c>
       <c r="C51" t="n">
-        <v>0.5632</v>
+        <v>0.5743</v>
       </c>
       <c r="D51" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0028</v>
       </c>
       <c r="E51" t="n">
-        <v>1.3538</v>
+        <v>1.3805</v>
       </c>
       <c r="F51" t="n">
-        <v>1.3538</v>
+        <v>2.0744</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>-0.6309</v>
       </c>
       <c r="H51" t="n">
-        <v>1.3538</v>
+        <v>2.0744</v>
       </c>
       <c r="I51" t="n">
-        <v>1.3538</v>
+        <v>2.1279</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>-0.6309</v>
       </c>
       <c r="K51" t="n">
-        <v>198</v>
+        <v>252</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="M51" t="n">
-        <v>1.3538</v>
+        <v>1.497</v>
       </c>
       <c r="N51" t="n">
-        <v>198</v>
+        <v>308</v>
       </c>
     </row>
     <row r="52">
@@ -2796,28 +2796,28 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>1.1232</v>
+        <v>1.1678</v>
       </c>
       <c r="C52" t="n">
-        <v>0.4673</v>
+        <v>0.4858</v>
       </c>
       <c r="D52" t="n">
-        <v>-0.1129</v>
+        <v>-0.0922</v>
       </c>
       <c r="E52" t="n">
-        <v>1.1232</v>
+        <v>1.1678</v>
       </c>
       <c r="F52" t="n">
-        <v>1.1232</v>
+        <v>1.1229</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>1.1232</v>
+        <v>1.1229</v>
       </c>
       <c r="I52" t="n">
-        <v>1.1232</v>
+        <v>1.1229</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
@@ -2829,7 +2829,7 @@
         <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>1.1232</v>
+        <v>1.1229</v>
       </c>
       <c r="N52" t="n">
         <v>256</v>
@@ -2842,16 +2842,16 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>1.0845</v>
+        <v>1.1396</v>
       </c>
       <c r="C53" t="n">
-        <v>0.4512</v>
+        <v>0.4741</v>
       </c>
       <c r="D53" t="n">
-        <v>-0.1305</v>
+        <v>-0.1048</v>
       </c>
       <c r="E53" t="n">
-        <v>1.0845</v>
+        <v>1.1396</v>
       </c>
       <c r="F53" t="n">
         <v>0.8527</v>
@@ -2884,369 +2884,369 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>saadzin</t>
+          <t>Alkaren</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.983</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>0.4089</v>
+        <v>0.3655</v>
       </c>
       <c r="D54" t="n">
-        <v>-0.1767</v>
+        <v>-0.2214</v>
       </c>
       <c r="E54" t="n">
-        <v>0.983</v>
+        <v>0.8784999999999999</v>
       </c>
       <c r="F54" t="n">
-        <v>0.983</v>
+        <v>0.7411</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.983</v>
+        <v>0.7411</v>
       </c>
       <c r="I54" t="n">
-        <v>0.983</v>
+        <v>0.7411</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
       </c>
       <c r="M54" t="n">
-        <v>0.983</v>
+        <v>0.7411</v>
       </c>
       <c r="N54" t="n">
-        <v>198</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ztr</t>
+          <t>saadzin</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.9431</v>
+        <v>0.8315</v>
       </c>
       <c r="C55" t="n">
-        <v>0.3923</v>
+        <v>0.3459</v>
       </c>
       <c r="D55" t="n">
-        <v>-0.1949</v>
+        <v>-0.2424</v>
       </c>
       <c r="E55" t="n">
-        <v>0.9431</v>
+        <v>0.8315</v>
       </c>
       <c r="F55" t="n">
-        <v>0.9431</v>
+        <v>0.9829</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>0.9431</v>
+        <v>0.9829</v>
       </c>
       <c r="I55" t="n">
-        <v>0.9431</v>
+        <v>0.9829</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
       <c r="L55" t="n">
         <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>0.9431</v>
+        <v>0.9829</v>
       </c>
       <c r="N55" t="n">
-        <v>242</v>
+        <v>198</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Alkaren</t>
+          <t>ztr</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7259</v>
+        <v>0.7006</v>
       </c>
       <c r="C56" t="n">
-        <v>0.302</v>
+        <v>0.2915</v>
       </c>
       <c r="D56" t="n">
-        <v>-0.2938</v>
+        <v>-0.3009</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7259</v>
+        <v>0.7006</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7259</v>
+        <v>0.9244</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>0.7259</v>
+        <v>0.9244</v>
       </c>
       <c r="I56" t="n">
-        <v>0.7259</v>
+        <v>0.9244</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
       <c r="L56" t="n">
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7259</v>
+        <v>0.9244</v>
       </c>
       <c r="N56" t="n">
-        <v>223</v>
+        <v>242</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Attacker</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.4334</v>
+        <v>0.497</v>
       </c>
       <c r="C57" t="n">
-        <v>0.1803</v>
+        <v>0.2068</v>
       </c>
       <c r="D57" t="n">
-        <v>-0.4269</v>
+        <v>-0.3918</v>
       </c>
       <c r="E57" t="n">
-        <v>0.4334</v>
+        <v>0.497</v>
       </c>
       <c r="F57" t="n">
-        <v>0.4334</v>
+        <v>0.3695</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0.4334</v>
+        <v>0.3695</v>
       </c>
       <c r="I57" t="n">
-        <v>0.4334</v>
+        <v>0.3695</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>212</v>
+        <v>146</v>
       </c>
       <c r="L57" t="n">
         <v>0</v>
       </c>
       <c r="M57" t="n">
-        <v>0.4334</v>
+        <v>0.3695</v>
       </c>
       <c r="N57" t="n">
-        <v>212</v>
+        <v>146</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Ex3rcice</t>
+          <t>Attacker</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.4137</v>
+        <v>0.4134</v>
       </c>
       <c r="C58" t="n">
-        <v>0.1721</v>
+        <v>0.172</v>
       </c>
       <c r="D58" t="n">
-        <v>-0.4359</v>
+        <v>-0.4292</v>
       </c>
       <c r="E58" t="n">
-        <v>0.4137</v>
+        <v>0.4134</v>
       </c>
       <c r="F58" t="n">
-        <v>0.4137</v>
+        <v>0.4332</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.4137</v>
+        <v>0.4332</v>
       </c>
       <c r="I58" t="n">
-        <v>0.4137</v>
+        <v>0.4332</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>262</v>
+        <v>212</v>
       </c>
       <c r="L58" t="n">
         <v>0</v>
       </c>
       <c r="M58" t="n">
-        <v>0.4137</v>
+        <v>0.4332</v>
       </c>
       <c r="N58" t="n">
-        <v>262</v>
+        <v>212</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FalleN</t>
+          <t>Ex3rcice</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.3748</v>
+        <v>0.4065</v>
       </c>
       <c r="C59" t="n">
-        <v>0.1559</v>
+        <v>0.1691</v>
       </c>
       <c r="D59" t="n">
-        <v>-0.4536</v>
+        <v>-0.4322</v>
       </c>
       <c r="E59" t="n">
-        <v>0.3748</v>
+        <v>0.4065</v>
       </c>
       <c r="F59" t="n">
-        <v>1.1392</v>
+        <v>0.4137</v>
       </c>
       <c r="G59" t="n">
-        <v>-0.7644</v>
+        <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>1.1392</v>
+        <v>0.4137</v>
       </c>
       <c r="I59" t="n">
-        <v>1.1392</v>
+        <v>0.4137</v>
       </c>
       <c r="J59" t="n">
-        <v>-0.7644</v>
+        <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="L59" t="n">
-        <v>229</v>
+        <v>0</v>
       </c>
       <c r="M59" t="n">
-        <v>0.3748</v>
+        <v>0.4137</v>
       </c>
       <c r="N59" t="n">
-        <v>427</v>
+        <v>262</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>malbsMd</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.3691</v>
+        <v>0.316</v>
       </c>
       <c r="C60" t="n">
-        <v>0.1535</v>
+        <v>0.1315</v>
       </c>
       <c r="D60" t="n">
-        <v>-0.4562</v>
+        <v>-0.4727</v>
       </c>
       <c r="E60" t="n">
-        <v>0.3691</v>
+        <v>0.316</v>
       </c>
       <c r="F60" t="n">
-        <v>0.3691</v>
+        <v>-0.5361</v>
       </c>
       <c r="G60" t="n">
-        <v>0</v>
+        <v>0.8768</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3691</v>
+        <v>-0.5361</v>
       </c>
       <c r="I60" t="n">
-        <v>0.3691</v>
+        <v>-0.5361</v>
       </c>
       <c r="J60" t="n">
-        <v>0</v>
+        <v>0.8768</v>
       </c>
       <c r="K60" t="n">
-        <v>146</v>
+        <v>185</v>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="M60" t="n">
-        <v>0.3691</v>
+        <v>0.3407</v>
       </c>
       <c r="N60" t="n">
-        <v>146</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>malbsMd</t>
+          <t>FalleN</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.3177</v>
+        <v>0.1184</v>
       </c>
       <c r="C61" t="n">
-        <v>0.1322</v>
+        <v>0.0493</v>
       </c>
       <c r="D61" t="n">
-        <v>-0.4796</v>
+        <v>-0.5609</v>
       </c>
       <c r="E61" t="n">
-        <v>0.3177</v>
+        <v>0.1184</v>
       </c>
       <c r="F61" t="n">
-        <v>-0.5593</v>
+        <v>1.1385</v>
       </c>
       <c r="G61" t="n">
-        <v>0.877</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="H61" t="n">
-        <v>-0.5593</v>
+        <v>1.1385</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5593</v>
+        <v>1.1385</v>
       </c>
       <c r="J61" t="n">
-        <v>0.877</v>
+        <v>-0.7645999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="L61" t="n">
-        <v>66</v>
+        <v>229</v>
       </c>
       <c r="M61" t="n">
-        <v>0.3177</v>
+        <v>0.3739000000000001</v>
       </c>
       <c r="N61" t="n">
-        <v>251</v>
+        <v>427</v>
       </c>
     </row>
     <row r="62">
@@ -3256,28 +3256,28 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.1983</v>
+        <v>0.0057</v>
       </c>
       <c r="C62" t="n">
-        <v>0.0825</v>
+        <v>0.0024</v>
       </c>
       <c r="D62" t="n">
-        <v>-0.5339</v>
+        <v>-0.6113</v>
       </c>
       <c r="E62" t="n">
-        <v>0.1983</v>
+        <v>0.0057</v>
       </c>
       <c r="F62" t="n">
-        <v>0.1983</v>
+        <v>0.2082</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.1983</v>
+        <v>0.2082</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1983</v>
+        <v>0.2082</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -3289,7 +3289,7 @@
         <v>0</v>
       </c>
       <c r="M62" t="n">
-        <v>0.1983</v>
+        <v>0.2082</v>
       </c>
       <c r="N62" t="n">
         <v>212</v>
@@ -3298,93 +3298,93 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>C4LLM3SU3</t>
+          <t>Graviti</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.1609</v>
+        <v>-0.0602</v>
       </c>
       <c r="C63" t="n">
-        <v>0.0669</v>
+        <v>-0.025</v>
       </c>
       <c r="D63" t="n">
-        <v>-0.551</v>
+        <v>-0.6407</v>
       </c>
       <c r="E63" t="n">
-        <v>0.1609</v>
+        <v>-0.0602</v>
       </c>
       <c r="F63" t="n">
-        <v>0.1609</v>
+        <v>0.0534</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>0.1609</v>
+        <v>0.0534</v>
       </c>
       <c r="I63" t="n">
-        <v>0.1609</v>
+        <v>0.0534</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>146</v>
+        <v>262</v>
       </c>
       <c r="L63" t="n">
         <v>0</v>
       </c>
       <c r="M63" t="n">
-        <v>0.1609</v>
+        <v>0.0534</v>
       </c>
       <c r="N63" t="n">
-        <v>146</v>
+        <v>262</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Graviti</t>
+          <t>C4LLM3SU3</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.0536</v>
+        <v>-0.1453</v>
       </c>
       <c r="C64" t="n">
-        <v>0.0223</v>
+        <v>-0.0604</v>
       </c>
       <c r="D64" t="n">
-        <v>-0.5998</v>
+        <v>-0.6787</v>
       </c>
       <c r="E64" t="n">
-        <v>0.0536</v>
+        <v>-0.1453</v>
       </c>
       <c r="F64" t="n">
-        <v>0.0536</v>
+        <v>0.152</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0.0536</v>
+        <v>0.152</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0536</v>
+        <v>0.152</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>262</v>
+        <v>146</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0.0536</v>
+        <v>0.152</v>
       </c>
       <c r="N64" t="n">
-        <v>262</v>
+        <v>146</v>
       </c>
     </row>
     <row r="65">
@@ -3394,28 +3394,28 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>-0.0693</v>
+        <v>-0.1867</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.0288</v>
+        <v>-0.07770000000000001</v>
       </c>
       <c r="D65" t="n">
-        <v>-0.6558</v>
+        <v>-0.6972</v>
       </c>
       <c r="E65" t="n">
-        <v>-0.0693</v>
+        <v>-0.1867</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3072</v>
+        <v>0.3071</v>
       </c>
       <c r="G65" t="n">
         <v>-0.3765</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3072</v>
+        <v>0.3071</v>
       </c>
       <c r="I65" t="n">
-        <v>0.3151</v>
+        <v>0.315</v>
       </c>
       <c r="J65" t="n">
         <v>-0.3765</v>
@@ -3427,7 +3427,7 @@
         <v>56</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.06140000000000001</v>
+        <v>-0.0615</v>
       </c>
       <c r="N65" t="n">
         <v>308</v>
@@ -3440,28 +3440,28 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>-0.1503</v>
+        <v>-0.3369</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.0625</v>
+        <v>-0.1402</v>
       </c>
       <c r="D66" t="n">
-        <v>-0.6926</v>
+        <v>-0.7643</v>
       </c>
       <c r="E66" t="n">
-        <v>-0.1503</v>
+        <v>-0.3369</v>
       </c>
       <c r="F66" t="n">
-        <v>-0.1503</v>
+        <v>-0.1389</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.1503</v>
+        <v>-0.1389</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.1503</v>
+        <v>-0.1389</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -3473,7 +3473,7 @@
         <v>0</v>
       </c>
       <c r="M66" t="n">
-        <v>-0.1503</v>
+        <v>-0.1389</v>
       </c>
       <c r="N66" t="n">
         <v>262</v>
@@ -3486,16 +3486,16 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>-0.3816</v>
+        <v>-0.5864</v>
       </c>
       <c r="C67" t="n">
-        <v>-0.1587</v>
+        <v>-0.2439</v>
       </c>
       <c r="D67" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-0.8758</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.3816</v>
+        <v>-0.5864</v>
       </c>
       <c r="F67" t="n">
         <v>1.9647</v>
@@ -3528,47 +3528,47 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>LNZ</t>
+          <t>ICY</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>-0.8023</v>
+        <v>-1.0471</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.3338</v>
+        <v>-0.4356</v>
       </c>
       <c r="D68" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-1.0815</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.8023</v>
+        <v>-1.0471</v>
       </c>
       <c r="F68" t="n">
-        <v>-0.8023</v>
+        <v>-0.9434</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>-0.8023</v>
+        <v>-0.9434</v>
       </c>
       <c r="I68" t="n">
-        <v>-0.8023</v>
+        <v>-0.9434</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
       </c>
       <c r="K68" t="n">
-        <v>223</v>
+        <v>262</v>
       </c>
       <c r="L68" t="n">
         <v>0</v>
       </c>
       <c r="M68" t="n">
-        <v>-0.8023</v>
+        <v>-0.9434</v>
       </c>
       <c r="N68" t="n">
-        <v>223</v>
+        <v>262</v>
       </c>
     </row>
     <row r="69">
@@ -3578,28 +3578,28 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>-0.858</v>
+        <v>-1.1392</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.3569</v>
+        <v>-0.4739</v>
       </c>
       <c r="D69" t="n">
-        <v>-1.0148</v>
+        <v>-1.1227</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.858</v>
+        <v>-1.1392</v>
       </c>
       <c r="F69" t="n">
-        <v>-0.858</v>
+        <v>-0.9179</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>-0.858</v>
+        <v>-0.9179</v>
       </c>
       <c r="I69" t="n">
-        <v>-0.858</v>
+        <v>-0.9179</v>
       </c>
       <c r="J69" t="n">
         <v>0</v>
@@ -3611,7 +3611,7 @@
         <v>0</v>
       </c>
       <c r="M69" t="n">
-        <v>-0.858</v>
+        <v>-0.9179</v>
       </c>
       <c r="N69" t="n">
         <v>198</v>
@@ -3620,185 +3620,185 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ICY</t>
+          <t>LNZ</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>-0.9433</v>
+        <v>-1.209</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.3924</v>
+        <v>-0.5029</v>
       </c>
       <c r="D70" t="n">
-        <v>-1.0536</v>
+        <v>-1.1539</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.9433</v>
+        <v>-1.209</v>
       </c>
       <c r="F70" t="n">
-        <v>-0.9433</v>
+        <v>-0.8165</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>-0.9433</v>
+        <v>-0.8165</v>
       </c>
       <c r="I70" t="n">
-        <v>-0.9433</v>
+        <v>-0.8165</v>
       </c>
       <c r="J70" t="n">
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>262</v>
+        <v>223</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
       </c>
       <c r="M70" t="n">
-        <v>-0.9433</v>
+        <v>-0.8165</v>
       </c>
       <c r="N70" t="n">
-        <v>262</v>
+        <v>223</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>HooXi</t>
+          <t>Westmelon</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>-1.0391</v>
+        <v>-1.2607</v>
       </c>
       <c r="C71" t="n">
-        <v>-0.4323</v>
+        <v>-0.5245</v>
       </c>
       <c r="D71" t="n">
-        <v>-1.0972</v>
+        <v>-1.1769</v>
       </c>
       <c r="E71" t="n">
-        <v>-1.0391</v>
+        <v>-1.2607</v>
       </c>
       <c r="F71" t="n">
-        <v>-0.2621</v>
+        <v>-1.2026</v>
       </c>
       <c r="G71" t="n">
-        <v>-0.777</v>
+        <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>-0.2621</v>
+        <v>-1.2026</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.2689</v>
+        <v>-1.2026</v>
       </c>
       <c r="J71" t="n">
-        <v>-0.777</v>
+        <v>0</v>
       </c>
       <c r="K71" t="n">
-        <v>252</v>
+        <v>146</v>
       </c>
       <c r="L71" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="M71" t="n">
-        <v>-1.0459</v>
+        <v>-1.2026</v>
       </c>
       <c r="N71" t="n">
-        <v>308</v>
+        <v>146</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>snow</t>
+          <t>HooXi</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>-1.176</v>
+        <v>-1.2866</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.4892</v>
+        <v>-0.5352</v>
       </c>
       <c r="D72" t="n">
-        <v>-1.1595</v>
+        <v>-1.1885</v>
       </c>
       <c r="E72" t="n">
-        <v>-1.176</v>
+        <v>-1.2866</v>
       </c>
       <c r="F72" t="n">
-        <v>-0.176</v>
+        <v>-0.2623</v>
       </c>
       <c r="G72" t="n">
-        <v>-1</v>
+        <v>-0.777</v>
       </c>
       <c r="H72" t="n">
-        <v>-0.176</v>
+        <v>-0.2623</v>
       </c>
       <c r="I72" t="n">
-        <v>-0.176</v>
+        <v>-0.2691</v>
       </c>
       <c r="J72" t="n">
-        <v>-1</v>
+        <v>-0.777</v>
       </c>
       <c r="K72" t="n">
-        <v>286</v>
+        <v>252</v>
       </c>
       <c r="L72" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="M72" t="n">
-        <v>-1.176</v>
+        <v>-1.0461</v>
       </c>
       <c r="N72" t="n">
-        <v>322</v>
+        <v>308</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Westmelon</t>
+          <t>snow</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>-1.2029</v>
+        <v>-1.3853</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.5004</v>
+        <v>-0.5763</v>
       </c>
       <c r="D73" t="n">
-        <v>-1.1718</v>
+        <v>-1.2326</v>
       </c>
       <c r="E73" t="n">
-        <v>-1.2029</v>
+        <v>-1.3853</v>
       </c>
       <c r="F73" t="n">
-        <v>-1.2029</v>
+        <v>-0.1768</v>
       </c>
       <c r="G73" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="H73" t="n">
-        <v>-1.2029</v>
+        <v>-0.1768</v>
       </c>
       <c r="I73" t="n">
-        <v>-1.2029</v>
+        <v>-0.1768</v>
       </c>
       <c r="J73" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="K73" t="n">
-        <v>146</v>
+        <v>286</v>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="M73" t="n">
-        <v>-1.2029</v>
+        <v>-1.1768</v>
       </c>
       <c r="N73" t="n">
-        <v>146</v>
+        <v>322</v>
       </c>
     </row>
     <row r="74">
@@ -3808,22 +3808,22 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>-1.5726</v>
+        <v>-1.53</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.6542</v>
+        <v>-0.6365</v>
       </c>
       <c r="D74" t="n">
-        <v>-1.3401</v>
+        <v>-1.2972</v>
       </c>
       <c r="E74" t="n">
-        <v>-1.5726</v>
+        <v>-1.53</v>
       </c>
       <c r="F74" t="n">
         <v>-0.8865</v>
       </c>
       <c r="G74" t="n">
-        <v>-0.6861</v>
+        <v>-0.6859</v>
       </c>
       <c r="H74" t="n">
         <v>-0.8865</v>
@@ -3832,7 +3832,7 @@
         <v>-0.8865</v>
       </c>
       <c r="J74" t="n">
-        <v>-0.6861</v>
+        <v>-0.6859</v>
       </c>
       <c r="K74" t="n">
         <v>286</v>
@@ -3841,7 +3841,7 @@
         <v>36</v>
       </c>
       <c r="M74" t="n">
-        <v>-1.5726</v>
+        <v>-1.5724</v>
       </c>
       <c r="N74" t="n">
         <v>322</v>
@@ -3854,28 +3854,28 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>-1.6137</v>
+        <v>-1.9164</v>
       </c>
       <c r="C75" t="n">
-        <v>-0.6713</v>
+        <v>-0.7972</v>
       </c>
       <c r="D75" t="n">
-        <v>-1.3588</v>
+        <v>-1.4698</v>
       </c>
       <c r="E75" t="n">
-        <v>-1.6137</v>
+        <v>-1.9164</v>
       </c>
       <c r="F75" t="n">
-        <v>-1.6137</v>
+        <v>-1.6136</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>-1.6137</v>
+        <v>-1.6136</v>
       </c>
       <c r="I75" t="n">
-        <v>-1.6137</v>
+        <v>-1.6136</v>
       </c>
       <c r="J75" t="n">
         <v>0</v>
@@ -3887,7 +3887,7 @@
         <v>0</v>
       </c>
       <c r="M75" t="n">
-        <v>-1.6137</v>
+        <v>-1.6136</v>
       </c>
       <c r="N75" t="n">
         <v>223</v>
@@ -3896,93 +3896,93 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>EmiliaQAQ</t>
+          <t>lux</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>-1.7518</v>
+        <v>-1.9632</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.7288</v>
+        <v>-0.8167</v>
       </c>
       <c r="D76" t="n">
-        <v>-1.4217</v>
+        <v>-1.4907</v>
       </c>
       <c r="E76" t="n">
-        <v>-1.7518</v>
+        <v>-1.9632</v>
       </c>
       <c r="F76" t="n">
-        <v>-1.7518</v>
+        <v>-1.7862</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>-1.7518</v>
+        <v>-1.7862</v>
       </c>
       <c r="I76" t="n">
-        <v>-1.7518</v>
+        <v>-1.7862</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>146</v>
+        <v>198</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
       </c>
       <c r="M76" t="n">
-        <v>-1.7518</v>
+        <v>-1.7862</v>
       </c>
       <c r="N76" t="n">
-        <v>146</v>
+        <v>198</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>lux</t>
+          <t>EmiliaQAQ</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>-1.7858</v>
+        <v>-1.9798</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.7429</v>
+        <v>-0.8236</v>
       </c>
       <c r="D77" t="n">
-        <v>-1.4371</v>
+        <v>-1.4982</v>
       </c>
       <c r="E77" t="n">
-        <v>-1.7858</v>
+        <v>-1.9798</v>
       </c>
       <c r="F77" t="n">
-        <v>-1.7858</v>
+        <v>-1.7514</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>-1.7858</v>
+        <v>-1.7514</v>
       </c>
       <c r="I77" t="n">
-        <v>-1.7858</v>
+        <v>-1.7514</v>
       </c>
       <c r="J77" t="n">
         <v>0</v>
       </c>
       <c r="K77" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
       </c>
       <c r="M77" t="n">
-        <v>-1.7858</v>
+        <v>-1.7514</v>
       </c>
       <c r="N77" t="n">
-        <v>198</v>
+        <v>146</v>
       </c>
     </row>
     <row r="78">
@@ -3992,28 +3992,28 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>-1.9969</v>
+        <v>-2.1694</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.8307</v>
+        <v>-0.9025</v>
       </c>
       <c r="D78" t="n">
-        <v>-1.5332</v>
+        <v>-1.5828</v>
       </c>
       <c r="E78" t="n">
-        <v>-1.9969</v>
+        <v>-2.1694</v>
       </c>
       <c r="F78" t="n">
-        <v>-2.4696</v>
+        <v>-2.4698</v>
       </c>
       <c r="G78" t="n">
         <v>0.4727</v>
       </c>
       <c r="H78" t="n">
-        <v>-2.4696</v>
+        <v>-2.4698</v>
       </c>
       <c r="I78" t="n">
-        <v>-2.5332</v>
+        <v>-2.5334</v>
       </c>
       <c r="J78" t="n">
         <v>0.4727</v>
@@ -4025,7 +4025,7 @@
         <v>95</v>
       </c>
       <c r="M78" t="n">
-        <v>-2.0605</v>
+        <v>-2.0607</v>
       </c>
       <c r="N78" t="n">
         <v>364</v>
@@ -4038,28 +4038,28 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>-2.0112</v>
+        <v>-2.3376</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.8367</v>
+        <v>-0.9725</v>
       </c>
       <c r="D79" t="n">
-        <v>-1.5397</v>
+        <v>-1.658</v>
       </c>
       <c r="E79" t="n">
-        <v>-2.0112</v>
+        <v>-2.3376</v>
       </c>
       <c r="F79" t="n">
-        <v>-2.0112</v>
+        <v>-2.0343</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>-2.0112</v>
+        <v>-2.0343</v>
       </c>
       <c r="I79" t="n">
-        <v>-2.0112</v>
+        <v>-2.0343</v>
       </c>
       <c r="J79" t="n">
         <v>0</v>
@@ -4071,7 +4071,7 @@
         <v>0</v>
       </c>
       <c r="M79" t="n">
-        <v>-2.0112</v>
+        <v>-2.0343</v>
       </c>
       <c r="N79" t="n">
         <v>262</v>
@@ -4084,16 +4084,16 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>-3.9174</v>
+        <v>-4.5083</v>
       </c>
       <c r="C80" t="n">
-        <v>-1.6297</v>
+        <v>-1.8755</v>
       </c>
       <c r="D80" t="n">
-        <v>-2.4075</v>
+        <v>-2.6276</v>
       </c>
       <c r="E80" t="n">
-        <v>-3.9174</v>
+        <v>-4.5083</v>
       </c>
       <c r="F80" t="n">
         <v>-3.2665</v>
@@ -4130,28 +4130,28 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>-4.4048</v>
+        <v>-4.8233</v>
       </c>
       <c r="C81" t="n">
-        <v>-1.8324</v>
+        <v>-2.0065</v>
       </c>
       <c r="D81" t="n">
-        <v>-2.6294</v>
+        <v>-2.7683</v>
       </c>
       <c r="E81" t="n">
-        <v>-4.4048</v>
+        <v>-4.8233</v>
       </c>
       <c r="F81" t="n">
-        <v>-4.4048</v>
+        <v>-4.4049</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>-4.4048</v>
+        <v>-4.4049</v>
       </c>
       <c r="I81" t="n">
-        <v>-4.4048</v>
+        <v>-4.4049</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -4163,7 +4163,7 @@
         <v>0</v>
       </c>
       <c r="M81" t="n">
-        <v>-4.4048</v>
+        <v>-4.4049</v>
       </c>
       <c r="N81" t="n">
         <v>256</v>
@@ -5666,13 +5666,13 @@
         <v>22</v>
       </c>
       <c r="H37" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="I37" t="n">
-        <v>0.4474</v>
+        <v>0.4597</v>
       </c>
       <c r="J37" t="n">
-        <v>9.8428</v>
+        <v>10.1134</v>
       </c>
     </row>
     <row r="38">
@@ -5709,10 +5709,10 @@
         <v>1.09</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1939</v>
+        <v>0.1935</v>
       </c>
       <c r="J38" t="n">
-        <v>4.2658</v>
+        <v>4.257</v>
       </c>
     </row>
     <row r="39">
@@ -5749,10 +5749,10 @@
         <v>0.96</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.06809999999999999</v>
+        <v>-0.0683</v>
       </c>
       <c r="J39" t="n">
-        <v>-1.4982</v>
+        <v>-1.5026</v>
       </c>
     </row>
     <row r="40">
@@ -5789,10 +5789,10 @@
         <v>0.68</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.3593</v>
+        <v>-0.3595</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.9046</v>
+        <v>-7.909</v>
       </c>
     </row>
     <row r="41">
@@ -5829,10 +5829,10 @@
         <v>0.64</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.3955</v>
+        <v>-0.3957</v>
       </c>
       <c r="J41" t="n">
-        <v>-8.701000000000001</v>
+        <v>-8.705399999999999</v>
       </c>
     </row>
     <row r="42">
@@ -6469,10 +6469,10 @@
         <v>1.32</v>
       </c>
       <c r="I57" t="n">
-        <v>0.5846</v>
+        <v>0.5851</v>
       </c>
       <c r="J57" t="n">
-        <v>16.3688</v>
+        <v>16.3828</v>
       </c>
     </row>
     <row r="58">
@@ -6509,10 +6509,10 @@
         <v>0.95</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.0843</v>
+        <v>-0.0842</v>
       </c>
       <c r="J58" t="n">
-        <v>-2.3604</v>
+        <v>-2.3576</v>
       </c>
     </row>
     <row r="59">
@@ -6549,10 +6549,10 @@
         <v>0.91</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.1334</v>
+        <v>-0.1332</v>
       </c>
       <c r="J59" t="n">
-        <v>-3.7352</v>
+        <v>-3.7296</v>
       </c>
     </row>
     <row r="60">
@@ -6589,10 +6589,10 @@
         <v>0.89</v>
       </c>
       <c r="I60" t="n">
-        <v>-0.1561</v>
+        <v>-0.156</v>
       </c>
       <c r="J60" t="n">
-        <v>-4.3708</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="61">
@@ -6626,13 +6626,13 @@
         <v>28</v>
       </c>
       <c r="H61" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.2402</v>
+        <v>-0.25</v>
       </c>
       <c r="J61" t="n">
-        <v>-6.7256</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="62">
@@ -8269,10 +8269,10 @@
         <v>1.77</v>
       </c>
       <c r="I102" t="n">
-        <v>1.2658</v>
+        <v>1.2662</v>
       </c>
       <c r="J102" t="n">
-        <v>21.5186</v>
+        <v>21.5254</v>
       </c>
     </row>
     <row r="103">
@@ -8306,13 +8306,13 @@
         <v>17</v>
       </c>
       <c r="H103" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I103" t="n">
-        <v>1.1543</v>
+        <v>1.1421</v>
       </c>
       <c r="J103" t="n">
-        <v>19.6231</v>
+        <v>19.4157</v>
       </c>
     </row>
     <row r="104">
@@ -8349,10 +8349,10 @@
         <v>1.45</v>
       </c>
       <c r="I104" t="n">
-        <v>0.8582</v>
+        <v>0.8584000000000001</v>
       </c>
       <c r="J104" t="n">
-        <v>14.5894</v>
+        <v>14.5928</v>
       </c>
     </row>
     <row r="105">
@@ -8389,10 +8389,10 @@
         <v>1.11</v>
       </c>
       <c r="I105" t="n">
-        <v>0.3039</v>
+        <v>0.3042</v>
       </c>
       <c r="J105" t="n">
-        <v>5.1663</v>
+        <v>5.1714</v>
       </c>
     </row>
     <row r="106">
@@ -8429,10 +8429,10 @@
         <v>1</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.0663</v>
+        <v>-0.066</v>
       </c>
       <c r="J106" t="n">
-        <v>-1.1271</v>
+        <v>-1.122</v>
       </c>
     </row>
     <row r="107">
@@ -8666,13 +8666,13 @@
         <v>19</v>
       </c>
       <c r="H112" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="I112" t="n">
-        <v>1.337</v>
+        <v>1.3256</v>
       </c>
       <c r="J112" t="n">
-        <v>25.403</v>
+        <v>25.1864</v>
       </c>
     </row>
     <row r="113">
@@ -8706,13 +8706,13 @@
         <v>19</v>
       </c>
       <c r="H113" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="I113" t="n">
-        <v>1.1347</v>
+        <v>1.1227</v>
       </c>
       <c r="J113" t="n">
-        <v>21.5593</v>
+        <v>21.3313</v>
       </c>
     </row>
     <row r="114">
@@ -8749,10 +8749,10 @@
         <v>1.2</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5078</v>
+        <v>0.5082</v>
       </c>
       <c r="J114" t="n">
-        <v>9.648199999999999</v>
+        <v>9.655799999999999</v>
       </c>
     </row>
     <row r="115">
@@ -8789,10 +8789,10 @@
         <v>1.05</v>
       </c>
       <c r="I115" t="n">
-        <v>0.1524</v>
+        <v>0.153</v>
       </c>
       <c r="J115" t="n">
-        <v>2.8956</v>
+        <v>2.907</v>
       </c>
     </row>
     <row r="116">
@@ -8829,10 +8829,10 @@
         <v>0.8</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.6414</v>
+        <v>-0.6408</v>
       </c>
       <c r="J116" t="n">
-        <v>-12.1866</v>
+        <v>-12.1752</v>
       </c>
     </row>
     <row r="117">
@@ -8869,10 +8869,10 @@
         <v>1.33</v>
       </c>
       <c r="I117" t="n">
-        <v>0.6163</v>
+        <v>0.6169</v>
       </c>
       <c r="J117" t="n">
-        <v>11.7097</v>
+        <v>11.7211</v>
       </c>
     </row>
     <row r="118">
@@ -8909,10 +8909,10 @@
         <v>1.13</v>
       </c>
       <c r="I118" t="n">
-        <v>0.3339</v>
+        <v>0.3344</v>
       </c>
       <c r="J118" t="n">
-        <v>6.3441</v>
+        <v>6.3536</v>
       </c>
     </row>
     <row r="119">
@@ -8949,10 +8949,10 @@
         <v>0.87</v>
       </c>
       <c r="I119" t="n">
-        <v>-0.1715</v>
+        <v>-0.1714</v>
       </c>
       <c r="J119" t="n">
-        <v>-3.2585</v>
+        <v>-3.2566</v>
       </c>
     </row>
     <row r="120">
@@ -8989,10 +8989,10 @@
         <v>0.63</v>
       </c>
       <c r="I120" t="n">
-        <v>-0.4017</v>
+        <v>-0.4015</v>
       </c>
       <c r="J120" t="n">
-        <v>-7.6323</v>
+        <v>-7.6285</v>
       </c>
     </row>
     <row r="121">
@@ -9026,13 +9026,13 @@
         <v>19</v>
       </c>
       <c r="H121" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.4807</v>
+        <v>-0.4892</v>
       </c>
       <c r="J121" t="n">
-        <v>-9.1333</v>
+        <v>-9.2948</v>
       </c>
     </row>
     <row r="122">
@@ -10666,13 +10666,13 @@
         <v>24</v>
       </c>
       <c r="H162" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5631</v>
+        <v>0.5743</v>
       </c>
       <c r="J162" t="n">
-        <v>13.5144</v>
+        <v>13.7832</v>
       </c>
     </row>
     <row r="163">
@@ -10709,10 +10709,10 @@
         <v>1.27</v>
       </c>
       <c r="I163" t="n">
-        <v>0.5164</v>
+        <v>0.516</v>
       </c>
       <c r="J163" t="n">
-        <v>12.3936</v>
+        <v>12.384</v>
       </c>
     </row>
     <row r="164">
@@ -10749,10 +10749,10 @@
         <v>0.93</v>
       </c>
       <c r="I164" t="n">
-        <v>-0.1133</v>
+        <v>-0.1135</v>
       </c>
       <c r="J164" t="n">
-        <v>-2.7192</v>
+        <v>-2.724</v>
       </c>
     </row>
     <row r="165">
@@ -10789,10 +10789,10 @@
         <v>0.87</v>
       </c>
       <c r="I165" t="n">
-        <v>-0.1821</v>
+        <v>-0.1823</v>
       </c>
       <c r="J165" t="n">
-        <v>-4.3704</v>
+        <v>-4.3752</v>
       </c>
     </row>
     <row r="166">
@@ -10829,10 +10829,10 @@
         <v>0.73</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.3218</v>
+        <v>-0.3219</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.7232</v>
+        <v>-7.7256</v>
       </c>
     </row>
     <row r="167">
@@ -10866,13 +10866,13 @@
         <v>24</v>
       </c>
       <c r="H167" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I167" t="n">
-        <v>1.2118</v>
+        <v>1.1998</v>
       </c>
       <c r="J167" t="n">
-        <v>29.0832</v>
+        <v>28.7952</v>
       </c>
     </row>
     <row r="168">
@@ -10909,10 +10909,10 @@
         <v>1.67</v>
       </c>
       <c r="I168" t="n">
-        <v>1.1985</v>
+        <v>1.1998</v>
       </c>
       <c r="J168" t="n">
-        <v>28.764</v>
+        <v>28.7952</v>
       </c>
     </row>
     <row r="169">
@@ -10949,10 +10949,10 @@
         <v>1.13</v>
       </c>
       <c r="I169" t="n">
-        <v>0.3925</v>
+        <v>0.393</v>
       </c>
       <c r="J169" t="n">
-        <v>9.42</v>
+        <v>9.432</v>
       </c>
     </row>
     <row r="170">
@@ -10989,10 +10989,10 @@
         <v>0.7</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8366</v>
       </c>
       <c r="J170" t="n">
-        <v>-20.0928</v>
+        <v>-20.0784</v>
       </c>
     </row>
     <row r="171">
@@ -11026,13 +11026,13 @@
         <v>24</v>
       </c>
       <c r="H171" t="n">
-        <v>0.58</v>
+        <v>0.57</v>
       </c>
       <c r="I171" t="n">
-        <v>-1.083</v>
+        <v>-1.1023</v>
       </c>
       <c r="J171" t="n">
-        <v>-25.992</v>
+        <v>-26.4552</v>
       </c>
     </row>
     <row r="172">
@@ -11666,13 +11666,13 @@
         <v>22</v>
       </c>
       <c r="H187" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1932</v>
+        <v>1.2064</v>
       </c>
       <c r="J187" t="n">
-        <v>26.2504</v>
+        <v>26.5408</v>
       </c>
     </row>
     <row r="188">
@@ -11706,13 +11706,13 @@
         <v>22</v>
       </c>
       <c r="H188" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="I188" t="n">
-        <v>0.5676</v>
+        <v>0.5518</v>
       </c>
       <c r="J188" t="n">
-        <v>12.4872</v>
+        <v>12.1396</v>
       </c>
     </row>
     <row r="189">
@@ -11866,13 +11866,13 @@
         <v>18</v>
       </c>
       <c r="H192" t="n">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="I192" t="n">
-        <v>1.5891</v>
+        <v>1.5779</v>
       </c>
       <c r="J192" t="n">
-        <v>28.6038</v>
+        <v>28.4022</v>
       </c>
     </row>
     <row r="193">
@@ -11906,13 +11906,13 @@
         <v>18</v>
       </c>
       <c r="H193" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I193" t="n">
-        <v>1.1953</v>
+        <v>1.1829</v>
       </c>
       <c r="J193" t="n">
-        <v>21.5154</v>
+        <v>21.2922</v>
       </c>
     </row>
     <row r="194">
@@ -11949,10 +11949,10 @@
         <v>1.28</v>
       </c>
       <c r="I194" t="n">
-        <v>0.7017</v>
+        <v>0.7019</v>
       </c>
       <c r="J194" t="n">
-        <v>12.6306</v>
+        <v>12.6342</v>
       </c>
     </row>
     <row r="195">
@@ -11989,10 +11989,10 @@
         <v>0.98</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.1485</v>
+        <v>-0.1479</v>
       </c>
       <c r="J195" t="n">
-        <v>-2.673</v>
+        <v>-2.6622</v>
       </c>
     </row>
     <row r="196">
@@ -12029,10 +12029,10 @@
         <v>0.67</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9191</v>
+        <v>-0.9186</v>
       </c>
       <c r="J196" t="n">
-        <v>-16.5438</v>
+        <v>-16.5348</v>
       </c>
     </row>
     <row r="197">
@@ -13869,10 +13869,10 @@
         <v>1.16</v>
       </c>
       <c r="I242" t="n">
-        <v>0.4268</v>
+        <v>0.4259</v>
       </c>
       <c r="J242" t="n">
-        <v>8.1092</v>
+        <v>8.0921</v>
       </c>
     </row>
     <row r="243">
@@ -13909,10 +13909,10 @@
         <v>0.98</v>
       </c>
       <c r="I243" t="n">
-        <v>-0.0207</v>
+        <v>-0.021</v>
       </c>
       <c r="J243" t="n">
-        <v>-0.3933</v>
+        <v>-0.399</v>
       </c>
     </row>
     <row r="244">
@@ -13949,10 +13949,10 @@
         <v>0.97</v>
       </c>
       <c r="I244" t="n">
-        <v>-0.0369</v>
+        <v>-0.0373</v>
       </c>
       <c r="J244" t="n">
-        <v>-0.7010999999999999</v>
+        <v>-0.7087</v>
       </c>
     </row>
     <row r="245">
@@ -13986,13 +13986,13 @@
         <v>19</v>
       </c>
       <c r="H245" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="I245" t="n">
-        <v>-0.5056</v>
+        <v>-0.4971</v>
       </c>
       <c r="J245" t="n">
-        <v>-9.606400000000001</v>
+        <v>-9.444900000000001</v>
       </c>
     </row>
     <row r="246">
@@ -14029,10 +14029,10 @@
         <v>0.39</v>
       </c>
       <c r="I246" t="n">
-        <v>-0.5996</v>
+        <v>-0.5998</v>
       </c>
       <c r="J246" t="n">
-        <v>-11.3924</v>
+        <v>-11.3962</v>
       </c>
     </row>
     <row r="247">
@@ -15266,13 +15266,13 @@
         <v>21</v>
       </c>
       <c r="H277" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="I277" t="n">
-        <v>0.648</v>
+        <v>0.6624</v>
       </c>
       <c r="J277" t="n">
-        <v>13.608</v>
+        <v>13.9104</v>
       </c>
     </row>
     <row r="278">
@@ -15309,10 +15309,10 @@
         <v>0.97</v>
       </c>
       <c r="I278" t="n">
-        <v>-0.0547</v>
+        <v>-0.055</v>
       </c>
       <c r="J278" t="n">
-        <v>-1.1487</v>
+        <v>-1.155</v>
       </c>
     </row>
     <row r="279">
@@ -15346,13 +15346,13 @@
         <v>21</v>
       </c>
       <c r="H279" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="I279" t="n">
-        <v>-0.095</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="J279" t="n">
-        <v>-1.995</v>
+        <v>-1.7346</v>
       </c>
     </row>
     <row r="280">
@@ -15389,10 +15389,10 @@
         <v>0.8</v>
       </c>
       <c r="I280" t="n">
-        <v>-0.2468</v>
+        <v>-0.2472</v>
       </c>
       <c r="J280" t="n">
-        <v>-5.1828</v>
+        <v>-5.1912</v>
       </c>
     </row>
     <row r="281">
@@ -15429,10 +15429,10 @@
         <v>0.67</v>
       </c>
       <c r="I281" t="n">
-        <v>-0.3696</v>
+        <v>-0.37</v>
       </c>
       <c r="J281" t="n">
-        <v>-7.7616</v>
+        <v>-7.77</v>
       </c>
     </row>
     <row r="282">
@@ -15466,13 +15466,13 @@
         <v>17</v>
       </c>
       <c r="H282" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="I282" t="n">
-        <v>1.0816</v>
+        <v>1.1076</v>
       </c>
       <c r="J282" t="n">
-        <v>18.3872</v>
+        <v>18.8292</v>
       </c>
     </row>
     <row r="283">
@@ -15509,10 +15509,10 @@
         <v>1.41</v>
       </c>
       <c r="I283" t="n">
-        <v>0.9429999999999999</v>
+        <v>0.9424</v>
       </c>
       <c r="J283" t="n">
-        <v>16.031</v>
+        <v>16.0208</v>
       </c>
     </row>
     <row r="284">
@@ -15549,10 +15549,10 @@
         <v>1.34</v>
       </c>
       <c r="I284" t="n">
-        <v>0.8128</v>
+        <v>0.8124</v>
       </c>
       <c r="J284" t="n">
-        <v>13.8176</v>
+        <v>13.8108</v>
       </c>
     </row>
     <row r="285">
@@ -15589,10 +15589,10 @@
         <v>1.25</v>
       </c>
       <c r="I285" t="n">
-        <v>0.636</v>
+        <v>0.6355</v>
       </c>
       <c r="J285" t="n">
-        <v>10.812</v>
+        <v>10.8035</v>
       </c>
     </row>
     <row r="286">
@@ -15629,10 +15629,10 @@
         <v>1.12</v>
       </c>
       <c r="I286" t="n">
-        <v>0.3414</v>
+        <v>0.3407</v>
       </c>
       <c r="J286" t="n">
-        <v>5.8038</v>
+        <v>5.7919</v>
       </c>
     </row>
     <row r="287">
@@ -15669,10 +15669,10 @@
         <v>1.03</v>
       </c>
       <c r="I287" t="n">
-        <v>0.1596</v>
+        <v>0.1588</v>
       </c>
       <c r="J287" t="n">
-        <v>2.7132</v>
+        <v>2.6996</v>
       </c>
     </row>
     <row r="288">
@@ -15709,10 +15709,10 @@
         <v>0.87</v>
       </c>
       <c r="I288" t="n">
-        <v>-0.1582</v>
+        <v>-0.1585</v>
       </c>
       <c r="J288" t="n">
-        <v>-2.6894</v>
+        <v>-2.6945</v>
       </c>
     </row>
     <row r="289">
@@ -15746,13 +15746,13 @@
         <v>17</v>
       </c>
       <c r="H289" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="I289" t="n">
-        <v>-0.2688</v>
+        <v>-0.26</v>
       </c>
       <c r="J289" t="n">
-        <v>-4.5696</v>
+        <v>-4.42</v>
       </c>
     </row>
     <row r="290">
@@ -15789,10 +15789,10 @@
         <v>0.65</v>
       </c>
       <c r="I290" t="n">
-        <v>-0.369</v>
+        <v>-0.3692</v>
       </c>
       <c r="J290" t="n">
-        <v>-6.273</v>
+        <v>-6.2764</v>
       </c>
     </row>
     <row r="291">
@@ -15829,10 +15829,10 @@
         <v>0.51</v>
       </c>
       <c r="I291" t="n">
-        <v>-0.493</v>
+        <v>-0.4932</v>
       </c>
       <c r="J291" t="n">
-        <v>-8.381</v>
+        <v>-8.384399999999999</v>
       </c>
     </row>
     <row r="292">
@@ -16669,10 +16669,10 @@
         <v>1.52</v>
       </c>
       <c r="I312" t="n">
-        <v>0.6438</v>
+        <v>0.6442</v>
       </c>
       <c r="J312" t="n">
-        <v>14.1636</v>
+        <v>14.1724</v>
       </c>
     </row>
     <row r="313">
@@ -16709,10 +16709,10 @@
         <v>1.3</v>
       </c>
       <c r="I313" t="n">
-        <v>0.4121</v>
+        <v>0.4123</v>
       </c>
       <c r="J313" t="n">
-        <v>9.0662</v>
+        <v>9.070600000000001</v>
       </c>
     </row>
     <row r="314">
@@ -16786,13 +16786,13 @@
         <v>22</v>
       </c>
       <c r="H315" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="I315" t="n">
-        <v>0.2108</v>
+        <v>0.1974</v>
       </c>
       <c r="J315" t="n">
-        <v>4.6376</v>
+        <v>4.3428</v>
       </c>
     </row>
     <row r="316">
@@ -16829,10 +16829,10 @@
         <v>0.89</v>
       </c>
       <c r="I316" t="n">
-        <v>-0.1754</v>
+        <v>-0.1753</v>
       </c>
       <c r="J316" t="n">
-        <v>-3.8588</v>
+        <v>-3.8566</v>
       </c>
     </row>
     <row r="317">
@@ -17669,10 +17669,10 @@
         <v>1.66</v>
       </c>
       <c r="I337" t="n">
-        <v>1.3737</v>
+        <v>1.3729</v>
       </c>
       <c r="J337" t="n">
-        <v>32.9688</v>
+        <v>32.9496</v>
       </c>
     </row>
     <row r="338">
@@ -17709,10 +17709,10 @@
         <v>1.01</v>
       </c>
       <c r="I338" t="n">
-        <v>0.0549</v>
+        <v>0.0546</v>
       </c>
       <c r="J338" t="n">
-        <v>1.3176</v>
+        <v>1.3104</v>
       </c>
     </row>
     <row r="339">
@@ -17746,13 +17746,13 @@
         <v>24</v>
       </c>
       <c r="H339" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I339" t="n">
-        <v>-0.3219</v>
+        <v>-0.2947</v>
       </c>
       <c r="J339" t="n">
-        <v>-7.7256</v>
+        <v>-7.0728</v>
       </c>
     </row>
     <row r="340">
@@ -17789,10 +17789,10 @@
         <v>0.83</v>
       </c>
       <c r="I340" t="n">
-        <v>-0.5242</v>
+        <v>-0.5246</v>
       </c>
       <c r="J340" t="n">
-        <v>-12.5808</v>
+        <v>-12.5904</v>
       </c>
     </row>
     <row r="341">
@@ -17829,10 +17829,10 @@
         <v>0.76</v>
       </c>
       <c r="I341" t="n">
-        <v>-0.6852</v>
+        <v>-0.6856</v>
       </c>
       <c r="J341" t="n">
-        <v>-16.4448</v>
+        <v>-16.4544</v>
       </c>
     </row>
     <row r="342">
@@ -18469,10 +18469,10 @@
         <v>1.73</v>
       </c>
       <c r="I357" t="n">
-        <v>1.3897</v>
+        <v>1.3901</v>
       </c>
       <c r="J357" t="n">
-        <v>25.0146</v>
+        <v>25.0218</v>
       </c>
     </row>
     <row r="358">
@@ -18509,10 +18509,10 @@
         <v>1.29</v>
       </c>
       <c r="I358" t="n">
-        <v>0.7213000000000001</v>
+        <v>0.7215</v>
       </c>
       <c r="J358" t="n">
-        <v>12.9834</v>
+        <v>12.987</v>
       </c>
     </row>
     <row r="359">
@@ -18546,13 +18546,13 @@
         <v>18</v>
       </c>
       <c r="H359" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="I359" t="n">
-        <v>0.5357</v>
+        <v>0.5139</v>
       </c>
       <c r="J359" t="n">
-        <v>9.6426</v>
+        <v>9.2502</v>
       </c>
     </row>
     <row r="360">
@@ -18589,10 +18589,10 @@
         <v>1.09</v>
       </c>
       <c r="I360" t="n">
-        <v>0.271</v>
+        <v>0.2713</v>
       </c>
       <c r="J360" t="n">
-        <v>4.878</v>
+        <v>4.8834</v>
       </c>
     </row>
     <row r="361">
@@ -18629,10 +18629,10 @@
         <v>1.08</v>
       </c>
       <c r="I361" t="n">
-        <v>0.2437</v>
+        <v>0.244</v>
       </c>
       <c r="J361" t="n">
-        <v>4.3866</v>
+        <v>4.392</v>
       </c>
     </row>
     <row r="362">
@@ -19266,13 +19266,13 @@
         <v>18</v>
       </c>
       <c r="H377" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="I377" t="n">
-        <v>0.3797</v>
+        <v>0.3927</v>
       </c>
       <c r="J377" t="n">
-        <v>6.8346</v>
+        <v>7.0686</v>
       </c>
     </row>
     <row r="378">
@@ -19309,10 +19309,10 @@
         <v>1.15</v>
       </c>
       <c r="I378" t="n">
-        <v>0.2949</v>
+        <v>0.2944</v>
       </c>
       <c r="J378" t="n">
-        <v>5.3082</v>
+        <v>5.2992</v>
       </c>
     </row>
     <row r="379">
@@ -19349,10 +19349,10 @@
         <v>0.98</v>
       </c>
       <c r="I379" t="n">
-        <v>-0.0333</v>
+        <v>-0.0335</v>
       </c>
       <c r="J379" t="n">
-        <v>-0.5994</v>
+        <v>-0.603</v>
       </c>
     </row>
     <row r="380">
@@ -19389,10 +19389,10 @@
         <v>0.66</v>
       </c>
       <c r="I380" t="n">
-        <v>-0.3731</v>
+        <v>-0.3734</v>
       </c>
       <c r="J380" t="n">
-        <v>-6.7158</v>
+        <v>-6.7212</v>
       </c>
     </row>
     <row r="381">
@@ -19429,10 +19429,10 @@
         <v>0.42</v>
       </c>
       <c r="I381" t="n">
-        <v>-0.5813</v>
+        <v>-0.5815</v>
       </c>
       <c r="J381" t="n">
-        <v>-10.4634</v>
+        <v>-10.467</v>
       </c>
     </row>
     <row r="382">
@@ -20069,16 +20069,16 @@
         <v>1.85</v>
       </c>
       <c r="I397" t="n">
-        <v>0.9416</v>
+        <v>0.9412</v>
       </c>
       <c r="J397" t="n">
-        <v>16.9488</v>
+        <v>16.9416</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>REZ</t>
+          <t>Kursy</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -20106,19 +20106,19 @@
         <v>18</v>
       </c>
       <c r="H398" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="I398" t="n">
-        <v>0.3501</v>
+        <v>0.3612</v>
       </c>
       <c r="J398" t="n">
-        <v>6.3018</v>
+        <v>6.5016</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Kursy</t>
+          <t>REZ</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -20149,10 +20149,10 @@
         <v>1.24</v>
       </c>
       <c r="I399" t="n">
-        <v>0.3387</v>
+        <v>0.3385</v>
       </c>
       <c r="J399" t="n">
-        <v>6.0966</v>
+        <v>6.093</v>
       </c>
     </row>
     <row r="400">
@@ -20189,10 +20189,10 @@
         <v>1.14</v>
       </c>
       <c r="I400" t="n">
-        <v>0.2157</v>
+        <v>0.2155</v>
       </c>
       <c r="J400" t="n">
-        <v>3.8826</v>
+        <v>3.879</v>
       </c>
     </row>
     <row r="401">
@@ -20229,10 +20229,10 @@
         <v>1.06</v>
       </c>
       <c r="I401" t="n">
-        <v>0.0997</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="J401" t="n">
-        <v>1.7946</v>
+        <v>1.791</v>
       </c>
     </row>
     <row r="402">
@@ -21469,10 +21469,10 @@
         <v>1.18</v>
       </c>
       <c r="I432" t="n">
-        <v>0.4002</v>
+        <v>0.3997</v>
       </c>
       <c r="J432" t="n">
-        <v>12.006</v>
+        <v>11.991</v>
       </c>
     </row>
     <row r="433">
@@ -21506,13 +21506,13 @@
         <v>30</v>
       </c>
       <c r="H433" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="I433" t="n">
-        <v>0.3104</v>
+        <v>0.3284</v>
       </c>
       <c r="J433" t="n">
-        <v>9.311999999999999</v>
+        <v>9.852</v>
       </c>
     </row>
     <row r="434">
@@ -21549,10 +21549,10 @@
         <v>1.06</v>
       </c>
       <c r="I434" t="n">
-        <v>0.1708</v>
+        <v>0.1704</v>
       </c>
       <c r="J434" t="n">
-        <v>5.124</v>
+        <v>5.112</v>
       </c>
     </row>
     <row r="435">
@@ -21589,10 +21589,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I435" t="n">
-        <v>-0.2421</v>
+        <v>-0.2423</v>
       </c>
       <c r="J435" t="n">
-        <v>-7.263</v>
+        <v>-7.269</v>
       </c>
     </row>
     <row r="436">
@@ -21629,10 +21629,10 @@
         <v>0.8</v>
       </c>
       <c r="I436" t="n">
-        <v>-0.2521</v>
+        <v>-0.2522</v>
       </c>
       <c r="J436" t="n">
-        <v>-7.563</v>
+        <v>-7.566</v>
       </c>
     </row>
     <row r="437">
@@ -23669,10 +23669,10 @@
         <v>1.8</v>
       </c>
       <c r="I487" t="n">
-        <v>1.4317</v>
+        <v>1.4314</v>
       </c>
       <c r="J487" t="n">
-        <v>21.4755</v>
+        <v>21.471</v>
       </c>
     </row>
     <row r="488">
@@ -23709,10 +23709,10 @@
         <v>1.75</v>
       </c>
       <c r="I488" t="n">
-        <v>1.3716</v>
+        <v>1.3713</v>
       </c>
       <c r="J488" t="n">
-        <v>20.574</v>
+        <v>20.5695</v>
       </c>
     </row>
     <row r="489">
@@ -23749,10 +23749,10 @@
         <v>1.65</v>
       </c>
       <c r="I489" t="n">
-        <v>1.2495</v>
+        <v>1.2493</v>
       </c>
       <c r="J489" t="n">
-        <v>18.7425</v>
+        <v>18.7395</v>
       </c>
     </row>
     <row r="490">
@@ -23789,10 +23789,10 @@
         <v>1.17</v>
       </c>
       <c r="I490" t="n">
-        <v>0.4343</v>
+        <v>0.434</v>
       </c>
       <c r="J490" t="n">
-        <v>6.5145</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="491">
@@ -23826,13 +23826,13 @@
         <v>15</v>
       </c>
       <c r="H491" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I491" t="n">
-        <v>0.411</v>
+        <v>0.434</v>
       </c>
       <c r="J491" t="n">
-        <v>6.165</v>
+        <v>6.51</v>
       </c>
     </row>
     <row r="492">
@@ -23869,10 +23869,10 @@
         <v>0.98</v>
       </c>
       <c r="I492" t="n">
-        <v>-0.0157</v>
+        <v>-0.0161</v>
       </c>
       <c r="J492" t="n">
-        <v>-0.314</v>
+        <v>-0.322</v>
       </c>
     </row>
     <row r="493">
@@ -23909,10 +23909,10 @@
         <v>0.89</v>
       </c>
       <c r="I493" t="n">
-        <v>-0.137</v>
+        <v>-0.1374</v>
       </c>
       <c r="J493" t="n">
-        <v>-2.74</v>
+        <v>-2.748</v>
       </c>
     </row>
     <row r="494">
@@ -23946,13 +23946,13 @@
         <v>20</v>
       </c>
       <c r="H494" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="I494" t="n">
-        <v>-0.2879</v>
+        <v>-0.2789</v>
       </c>
       <c r="J494" t="n">
-        <v>-5.758</v>
+        <v>-5.578</v>
       </c>
     </row>
     <row r="495">
@@ -23989,10 +23989,10 @@
         <v>0.71</v>
       </c>
       <c r="I495" t="n">
-        <v>-0.3155</v>
+        <v>-0.3157</v>
       </c>
       <c r="J495" t="n">
-        <v>-6.31</v>
+        <v>-6.314</v>
       </c>
     </row>
     <row r="496">
@@ -24029,10 +24029,10 @@
         <v>0.55</v>
       </c>
       <c r="I496" t="n">
-        <v>-0.4591</v>
+        <v>-0.4594</v>
       </c>
       <c r="J496" t="n">
-        <v>-9.182</v>
+        <v>-9.188000000000001</v>
       </c>
     </row>
     <row r="497">
@@ -24069,10 +24069,10 @@
         <v>1.83</v>
       </c>
       <c r="I497" t="n">
-        <v>1.5042</v>
+        <v>1.5047</v>
       </c>
       <c r="J497" t="n">
-        <v>30.084</v>
+        <v>30.094</v>
       </c>
     </row>
     <row r="498">
@@ -24106,13 +24106,13 @@
         <v>20</v>
       </c>
       <c r="H498" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="I498" t="n">
-        <v>1.4918</v>
+        <v>1.48</v>
       </c>
       <c r="J498" t="n">
-        <v>29.836</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="499">
@@ -24149,10 +24149,10 @@
         <v>1.25</v>
       </c>
       <c r="I499" t="n">
-        <v>0.6363</v>
+        <v>0.6365</v>
       </c>
       <c r="J499" t="n">
-        <v>12.726</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="500">
@@ -24189,10 +24189,10 @@
         <v>1.03</v>
       </c>
       <c r="I500" t="n">
-        <v>0.0837</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="J500" t="n">
-        <v>1.674</v>
+        <v>1.68</v>
       </c>
     </row>
     <row r="501">
@@ -24229,10 +24229,10 @@
         <v>0.68</v>
       </c>
       <c r="I501" t="n">
-        <v>-0.904</v>
+        <v>-0.9038</v>
       </c>
       <c r="J501" t="n">
-        <v>-18.08</v>
+        <v>-18.076</v>
       </c>
     </row>
     <row r="502">
@@ -24269,10 +24269,10 @@
         <v>1.34</v>
       </c>
       <c r="I502" t="n">
-        <v>0.4595</v>
+        <v>0.4592</v>
       </c>
       <c r="J502" t="n">
-        <v>13.785</v>
+        <v>13.776</v>
       </c>
     </row>
     <row r="503">
@@ -24306,13 +24306,13 @@
         <v>30</v>
       </c>
       <c r="H503" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I503" t="n">
-        <v>0.3355</v>
+        <v>0.3469</v>
       </c>
       <c r="J503" t="n">
-        <v>10.065</v>
+        <v>10.407</v>
       </c>
     </row>
     <row r="504">
@@ -24389,10 +24389,10 @@
         <v>1.09</v>
       </c>
       <c r="I505" t="n">
-        <v>0.1575</v>
+        <v>0.1573</v>
       </c>
       <c r="J505" t="n">
-        <v>4.725</v>
+        <v>4.719</v>
       </c>
     </row>
     <row r="506">
@@ -24429,10 +24429,10 @@
         <v>1.06</v>
       </c>
       <c r="I506" t="n">
-        <v>0.1114</v>
+        <v>0.1112</v>
       </c>
       <c r="J506" t="n">
-        <v>3.342</v>
+        <v>3.336</v>
       </c>
     </row>
     <row r="507">
@@ -25869,10 +25869,10 @@
         <v>1.38</v>
       </c>
       <c r="I542" t="n">
-        <v>0.5482</v>
+        <v>0.5478</v>
       </c>
       <c r="J542" t="n">
-        <v>11.5122</v>
+        <v>11.5038</v>
       </c>
     </row>
     <row r="543">
@@ -25909,10 +25909,10 @@
         <v>1.22</v>
       </c>
       <c r="I543" t="n">
-        <v>0.3537</v>
+        <v>0.3534</v>
       </c>
       <c r="J543" t="n">
-        <v>7.4277</v>
+        <v>7.4214</v>
       </c>
     </row>
     <row r="544">
@@ -25946,13 +25946,13 @@
         <v>21</v>
       </c>
       <c r="H544" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="I544" t="n">
-        <v>0.2745</v>
+        <v>0.2878</v>
       </c>
       <c r="J544" t="n">
-        <v>5.7645</v>
+        <v>6.0438</v>
       </c>
     </row>
     <row r="545">
@@ -25989,10 +25989,10 @@
         <v>0.88</v>
       </c>
       <c r="I545" t="n">
-        <v>-0.1757</v>
+        <v>-0.1759</v>
       </c>
       <c r="J545" t="n">
-        <v>-3.6897</v>
+        <v>-3.6939</v>
       </c>
     </row>
     <row r="546">
@@ -26029,10 +26029,10 @@
         <v>0.73</v>
       </c>
       <c r="I546" t="n">
-        <v>-0.3261</v>
+        <v>-0.3263</v>
       </c>
       <c r="J546" t="n">
-        <v>-6.8481</v>
+        <v>-6.8523</v>
       </c>
     </row>
     <row r="547">
@@ -26066,13 +26066,13 @@
         <v>21</v>
       </c>
       <c r="H547" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="I547" t="n">
-        <v>0.5113</v>
+        <v>0.5009</v>
       </c>
       <c r="J547" t="n">
-        <v>10.7373</v>
+        <v>10.5189</v>
       </c>
     </row>
     <row r="548">
@@ -26109,10 +26109,10 @@
         <v>1.38</v>
       </c>
       <c r="I548" t="n">
-        <v>0.5006</v>
+        <v>0.5009</v>
       </c>
       <c r="J548" t="n">
-        <v>10.5126</v>
+        <v>10.5189</v>
       </c>
     </row>
     <row r="549">
@@ -26149,10 +26149,10 @@
         <v>1.22</v>
       </c>
       <c r="I549" t="n">
-        <v>0.3226</v>
+        <v>0.3227</v>
       </c>
       <c r="J549" t="n">
-        <v>6.7746</v>
+        <v>6.7767</v>
       </c>
     </row>
     <row r="550">
@@ -26189,10 +26189,10 @@
         <v>1.01</v>
       </c>
       <c r="I550" t="n">
-        <v>0.0148</v>
+        <v>0.015</v>
       </c>
       <c r="J550" t="n">
-        <v>0.3108</v>
+        <v>0.315</v>
       </c>
     </row>
     <row r="551">
@@ -26229,10 +26229,10 @@
         <v>0.98</v>
       </c>
       <c r="I551" t="n">
-        <v>-0.0577</v>
+        <v>-0.0575</v>
       </c>
       <c r="J551" t="n">
-        <v>-1.2117</v>
+        <v>-1.2075</v>
       </c>
     </row>
     <row r="552">
@@ -26469,10 +26469,10 @@
         <v>1.3</v>
       </c>
       <c r="I557" t="n">
-        <v>0.6014</v>
+        <v>0.6008</v>
       </c>
       <c r="J557" t="n">
-        <v>13.8322</v>
+        <v>13.8184</v>
       </c>
     </row>
     <row r="558">
@@ -26506,13 +26506,13 @@
         <v>23</v>
       </c>
       <c r="H558" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="I558" t="n">
-        <v>0.471</v>
+        <v>0.4872</v>
       </c>
       <c r="J558" t="n">
-        <v>10.833</v>
+        <v>11.2056</v>
       </c>
     </row>
     <row r="559">
@@ -26549,10 +26549,10 @@
         <v>0.98</v>
       </c>
       <c r="I559" t="n">
-        <v>-0.0419</v>
+        <v>-0.042</v>
       </c>
       <c r="J559" t="n">
-        <v>-0.9637</v>
+        <v>-0.966</v>
       </c>
     </row>
     <row r="560">
@@ -26589,10 +26589,10 @@
         <v>0.72</v>
       </c>
       <c r="I560" t="n">
-        <v>-0.3279</v>
+        <v>-0.3281</v>
       </c>
       <c r="J560" t="n">
-        <v>-7.5417</v>
+        <v>-7.5463</v>
       </c>
     </row>
     <row r="561">
@@ -26629,10 +26629,10 @@
         <v>0.71</v>
       </c>
       <c r="I561" t="n">
-        <v>-0.3372</v>
+        <v>-0.3374</v>
       </c>
       <c r="J561" t="n">
-        <v>-7.7556</v>
+        <v>-7.7602</v>
       </c>
     </row>
     <row r="562">
@@ -27069,10 +27069,10 @@
         <v>1.1</v>
       </c>
       <c r="I572" t="n">
-        <v>0.2702</v>
+        <v>0.2697</v>
       </c>
       <c r="J572" t="n">
-        <v>6.2146</v>
+        <v>6.2031</v>
       </c>
     </row>
     <row r="573">
@@ -27109,10 +27109,10 @@
         <v>0.97</v>
       </c>
       <c r="I573" t="n">
-        <v>-0.0528</v>
+        <v>-0.053</v>
       </c>
       <c r="J573" t="n">
-        <v>-1.2144</v>
+        <v>-1.219</v>
       </c>
     </row>
     <row r="574">
@@ -27149,10 +27149,10 @@
         <v>0.89</v>
       </c>
       <c r="I574" t="n">
-        <v>-0.1514</v>
+        <v>-0.1515</v>
       </c>
       <c r="J574" t="n">
-        <v>-3.4822</v>
+        <v>-3.4845</v>
       </c>
     </row>
     <row r="575">
@@ -27189,10 +27189,10 @@
         <v>0.83</v>
       </c>
       <c r="I575" t="n">
-        <v>-0.2146</v>
+        <v>-0.2148</v>
       </c>
       <c r="J575" t="n">
-        <v>-4.9358</v>
+        <v>-4.9404</v>
       </c>
     </row>
     <row r="576">
@@ -27226,13 +27226,13 @@
         <v>23</v>
       </c>
       <c r="H576" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="I576" t="n">
-        <v>-0.2447</v>
+        <v>-0.235</v>
       </c>
       <c r="J576" t="n">
-        <v>-5.6281</v>
+        <v>-5.405</v>
       </c>
     </row>
     <row r="577">
@@ -28158,7 +28158,7 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
@@ -28269,10 +28269,10 @@
         <v>1.47</v>
       </c>
       <c r="I602" t="n">
-        <v>1.0802</v>
+        <v>1.0807</v>
       </c>
       <c r="J602" t="n">
-        <v>24.8446</v>
+        <v>24.8561</v>
       </c>
     </row>
     <row r="603">
@@ -28309,10 +28309,10 @@
         <v>1.25</v>
       </c>
       <c r="I603" t="n">
-        <v>0.6649</v>
+        <v>0.6654</v>
       </c>
       <c r="J603" t="n">
-        <v>15.2927</v>
+        <v>15.3042</v>
       </c>
     </row>
     <row r="604">
@@ -28349,10 +28349,10 @@
         <v>1.2</v>
       </c>
       <c r="I604" t="n">
-        <v>0.556</v>
+        <v>0.5564</v>
       </c>
       <c r="J604" t="n">
-        <v>12.788</v>
+        <v>12.7972</v>
       </c>
     </row>
     <row r="605">
@@ -28389,10 +28389,10 @@
         <v>0.89</v>
       </c>
       <c r="I605" t="n">
-        <v>-0.3927</v>
+        <v>-0.3923</v>
       </c>
       <c r="J605" t="n">
-        <v>-9.0321</v>
+        <v>-9.0229</v>
       </c>
     </row>
     <row r="606">
@@ -28426,13 +28426,13 @@
         <v>23</v>
       </c>
       <c r="H606" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="I606" t="n">
-        <v>-0.5889</v>
+        <v>-0.6116</v>
       </c>
       <c r="J606" t="n">
-        <v>-13.5447</v>
+        <v>-14.0668</v>
       </c>
     </row>
     <row r="607">
@@ -28518,7 +28518,7 @@
     <row r="609">
       <c r="A609" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B609" t="inlineStr">
@@ -28669,10 +28669,10 @@
         <v>1.53</v>
       </c>
       <c r="I612" t="n">
-        <v>0.6936</v>
+        <v>0.6942</v>
       </c>
       <c r="J612" t="n">
-        <v>16.6464</v>
+        <v>16.6608</v>
       </c>
     </row>
     <row r="613">
@@ -28709,10 +28709,10 @@
         <v>1.13</v>
       </c>
       <c r="I613" t="n">
-        <v>0.227</v>
+        <v>0.2272</v>
       </c>
       <c r="J613" t="n">
-        <v>5.448</v>
+        <v>5.4528</v>
       </c>
     </row>
     <row r="614">
@@ -28746,13 +28746,13 @@
         <v>24</v>
       </c>
       <c r="H614" t="n">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="I614" t="n">
-        <v>-0.0598</v>
+        <v>-0.074</v>
       </c>
       <c r="J614" t="n">
-        <v>-1.4352</v>
+        <v>-1.776</v>
       </c>
     </row>
     <row r="615">
@@ -28789,10 +28789,10 @@
         <v>0.89</v>
       </c>
       <c r="I615" t="n">
-        <v>-0.1601</v>
+        <v>-0.16</v>
       </c>
       <c r="J615" t="n">
-        <v>-3.8424</v>
+        <v>-3.84</v>
       </c>
     </row>
     <row r="616">
@@ -28829,10 +28829,10 @@
         <v>0.59</v>
       </c>
       <c r="I616" t="n">
-        <v>-0.4477</v>
+        <v>-0.4475</v>
       </c>
       <c r="J616" t="n">
-        <v>-10.7448</v>
+        <v>-10.74</v>
       </c>
     </row>
     <row r="617">
@@ -31866,13 +31866,13 @@
         <v>19</v>
       </c>
       <c r="H692" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="I692" t="n">
-        <v>1.3642</v>
+        <v>1.3769</v>
       </c>
       <c r="J692" t="n">
-        <v>25.9198</v>
+        <v>26.1611</v>
       </c>
     </row>
     <row r="693">
@@ -31906,13 +31906,13 @@
         <v>19</v>
       </c>
       <c r="H693" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I693" t="n">
-        <v>0.9327</v>
+        <v>0.9142</v>
       </c>
       <c r="J693" t="n">
-        <v>17.7213</v>
+        <v>17.3698</v>
       </c>
     </row>
     <row r="694">
@@ -32669,10 +32669,10 @@
         <v>1.42</v>
       </c>
       <c r="I712" t="n">
-        <v>0.9874000000000001</v>
+        <v>0.9879</v>
       </c>
       <c r="J712" t="n">
-        <v>34.559</v>
+        <v>34.5765</v>
       </c>
     </row>
     <row r="713">
@@ -32709,10 +32709,10 @@
         <v>1.27</v>
       </c>
       <c r="I713" t="n">
-        <v>0.6942</v>
+        <v>0.6946</v>
       </c>
       <c r="J713" t="n">
-        <v>24.297</v>
+        <v>24.311</v>
       </c>
     </row>
     <row r="714">
@@ -32749,10 +32749,10 @@
         <v>1.18</v>
       </c>
       <c r="I714" t="n">
-        <v>0.5034</v>
+        <v>0.5036</v>
       </c>
       <c r="J714" t="n">
-        <v>17.619</v>
+        <v>17.626</v>
       </c>
     </row>
     <row r="715">
@@ -32789,10 +32789,10 @@
         <v>1.1</v>
       </c>
       <c r="I715" t="n">
-        <v>0.3125</v>
+        <v>0.3128</v>
       </c>
       <c r="J715" t="n">
-        <v>10.9375</v>
+        <v>10.948</v>
       </c>
     </row>
     <row r="716">
@@ -32826,13 +32826,13 @@
         <v>35</v>
       </c>
       <c r="H716" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="I716" t="n">
-        <v>-0.2029</v>
+        <v>-0.2344</v>
       </c>
       <c r="J716" t="n">
-        <v>-7.1015</v>
+        <v>-8.204000000000001</v>
       </c>
     </row>
     <row r="717">
@@ -33469,10 +33469,10 @@
         <v>1.54</v>
       </c>
       <c r="I732" t="n">
-        <v>0.9499</v>
+        <v>0.9492</v>
       </c>
       <c r="J732" t="n">
-        <v>22.7976</v>
+        <v>22.7808</v>
       </c>
     </row>
     <row r="733">
@@ -33509,10 +33509,10 @@
         <v>1.09</v>
       </c>
       <c r="I733" t="n">
-        <v>0.2307</v>
+        <v>0.2303</v>
       </c>
       <c r="J733" t="n">
-        <v>5.5368</v>
+        <v>5.5272</v>
       </c>
     </row>
     <row r="734">
@@ -33546,13 +33546,13 @@
         <v>24</v>
       </c>
       <c r="H734" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="I734" t="n">
-        <v>0.0425</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J734" t="n">
-        <v>1.02</v>
+        <v>1.728</v>
       </c>
     </row>
     <row r="735">
@@ -33589,10 +33589,10 @@
         <v>0.73</v>
       </c>
       <c r="I735" t="n">
-        <v>-0.3209</v>
+        <v>-0.3211</v>
       </c>
       <c r="J735" t="n">
-        <v>-7.7016</v>
+        <v>-7.7064</v>
       </c>
     </row>
     <row r="736">
@@ -33629,10 +33629,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I736" t="n">
-        <v>-0.3579</v>
+        <v>-0.3581</v>
       </c>
       <c r="J736" t="n">
-        <v>-8.589600000000001</v>
+        <v>-8.5944</v>
       </c>
     </row>
     <row r="737">
@@ -34069,10 +34069,10 @@
         <v>1.28</v>
       </c>
       <c r="I747" t="n">
-        <v>0.443</v>
+        <v>0.4426</v>
       </c>
       <c r="J747" t="n">
-        <v>10.189</v>
+        <v>10.1798</v>
       </c>
     </row>
     <row r="748">
@@ -34106,13 +34106,13 @@
         <v>23</v>
       </c>
       <c r="H748" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="I748" t="n">
-        <v>0.3792</v>
+        <v>0.3918</v>
       </c>
       <c r="J748" t="n">
-        <v>8.7216</v>
+        <v>9.0114</v>
       </c>
     </row>
     <row r="749">
@@ -34149,10 +34149,10 @@
         <v>1.1</v>
       </c>
       <c r="I749" t="n">
-        <v>0.1978</v>
+        <v>0.1975</v>
       </c>
       <c r="J749" t="n">
-        <v>4.5494</v>
+        <v>4.5425</v>
       </c>
     </row>
     <row r="750">
@@ -34189,10 +34189,10 @@
         <v>0.87</v>
       </c>
       <c r="I750" t="n">
-        <v>-0.1802</v>
+        <v>-0.1804</v>
       </c>
       <c r="J750" t="n">
-        <v>-4.1446</v>
+        <v>-4.1492</v>
       </c>
     </row>
     <row r="751">
@@ -34229,10 +34229,10 @@
         <v>0.52</v>
       </c>
       <c r="I751" t="n">
-        <v>-0.506</v>
+        <v>-0.5062</v>
       </c>
       <c r="J751" t="n">
-        <v>-11.638</v>
+        <v>-11.6426</v>
       </c>
     </row>
     <row r="752">
@@ -34869,10 +34869,10 @@
         <v>1.85</v>
       </c>
       <c r="I767" t="n">
-        <v>1.5313</v>
+        <v>1.5318</v>
       </c>
       <c r="J767" t="n">
-        <v>29.0947</v>
+        <v>29.1042</v>
       </c>
     </row>
     <row r="768">
@@ -34906,13 +34906,13 @@
         <v>19</v>
       </c>
       <c r="H768" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="I768" t="n">
-        <v>0.9449</v>
+        <v>0.9272</v>
       </c>
       <c r="J768" t="n">
-        <v>17.9531</v>
+        <v>17.6168</v>
       </c>
     </row>
     <row r="769">
@@ -34949,10 +34949,10 @@
         <v>1.22</v>
       </c>
       <c r="I769" t="n">
-        <v>0.5743</v>
+        <v>0.5746</v>
       </c>
       <c r="J769" t="n">
-        <v>10.9117</v>
+        <v>10.9174</v>
       </c>
     </row>
     <row r="770">
@@ -34989,10 +34989,10 @@
         <v>1.16</v>
       </c>
       <c r="I770" t="n">
-        <v>0.44</v>
+        <v>0.4403</v>
       </c>
       <c r="J770" t="n">
-        <v>8.359999999999999</v>
+        <v>8.3657</v>
       </c>
     </row>
     <row r="771">
@@ -35029,10 +35029,10 @@
         <v>0.92</v>
       </c>
       <c r="I771" t="n">
-        <v>-0.3442</v>
+        <v>-0.3439</v>
       </c>
       <c r="J771" t="n">
-        <v>-6.5398</v>
+        <v>-6.5341</v>
       </c>
     </row>
     <row r="772">
@@ -35278,7 +35278,7 @@
     <row r="778">
       <c r="A778" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B778" t="inlineStr">
@@ -35638,7 +35638,7 @@
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
@@ -37666,13 +37666,13 @@
         <v>21</v>
       </c>
       <c r="H837" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="I837" t="n">
-        <v>-0.1174</v>
+        <v>-0.1056</v>
       </c>
       <c r="J837" t="n">
-        <v>-2.4654</v>
+        <v>-2.2176</v>
       </c>
     </row>
     <row r="838">
@@ -37709,10 +37709,10 @@
         <v>0.86</v>
       </c>
       <c r="I838" t="n">
-        <v>-0.174</v>
+        <v>-0.1743</v>
       </c>
       <c r="J838" t="n">
-        <v>-3.654</v>
+        <v>-3.6603</v>
       </c>
     </row>
     <row r="839">
@@ -37749,10 +37749,10 @@
         <v>0.84</v>
       </c>
       <c r="I839" t="n">
-        <v>-0.195</v>
+        <v>-0.1952</v>
       </c>
       <c r="J839" t="n">
-        <v>-4.095</v>
+        <v>-4.0992</v>
       </c>
     </row>
     <row r="840">
@@ -37789,10 +37789,10 @@
         <v>0.73</v>
       </c>
       <c r="I840" t="n">
-        <v>-0.2998</v>
+        <v>-0.3</v>
       </c>
       <c r="J840" t="n">
-        <v>-6.2958</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="841">
@@ -37829,10 +37829,10 @@
         <v>0.66</v>
       </c>
       <c r="I841" t="n">
-        <v>-0.3641</v>
+        <v>-0.3643</v>
       </c>
       <c r="J841" t="n">
-        <v>-7.6461</v>
+        <v>-7.6503</v>
       </c>
     </row>
     <row r="842">
@@ -38066,13 +38066,13 @@
         <v>23</v>
       </c>
       <c r="H847" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="I847" t="n">
-        <v>0.7719</v>
+        <v>0.7581</v>
       </c>
       <c r="J847" t="n">
-        <v>17.7537</v>
+        <v>17.4363</v>
       </c>
     </row>
     <row r="848">
@@ -38109,10 +38109,10 @@
         <v>0.96</v>
       </c>
       <c r="I848" t="n">
-        <v>-0.0692</v>
+        <v>-0.0689</v>
       </c>
       <c r="J848" t="n">
-        <v>-1.5916</v>
+        <v>-1.5847</v>
       </c>
     </row>
     <row r="849">
@@ -38149,16 +38149,16 @@
         <v>0.83</v>
       </c>
       <c r="I849" t="n">
-        <v>-0.2169</v>
+        <v>-0.2165</v>
       </c>
       <c r="J849" t="n">
-        <v>-4.9887</v>
+        <v>-4.9795</v>
       </c>
     </row>
     <row r="850">
       <c r="A850" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B850" t="inlineStr">
@@ -38189,10 +38189,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I850" t="n">
-        <v>-0.2371</v>
+        <v>-0.2367</v>
       </c>
       <c r="J850" t="n">
-        <v>-5.4533</v>
+        <v>-5.4441</v>
       </c>
     </row>
     <row r="851">
@@ -38226,13 +38226,13 @@
         <v>23</v>
       </c>
       <c r="H851" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="I851" t="n">
-        <v>-0.3331</v>
+        <v>-0.342</v>
       </c>
       <c r="J851" t="n">
-        <v>-7.6613</v>
+        <v>-7.866</v>
       </c>
     </row>
     <row r="852">
@@ -38478,7 +38478,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>z4kr</t>
+          <t>z4KR</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -39066,13 +39066,13 @@
         <v>29</v>
       </c>
       <c r="H872" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="I872" t="n">
-        <v>0.7581</v>
+        <v>0.7727000000000001</v>
       </c>
       <c r="J872" t="n">
-        <v>21.9849</v>
+        <v>22.4083</v>
       </c>
     </row>
     <row r="873">
@@ -39109,10 +39109,10 @@
         <v>0.91</v>
       </c>
       <c r="I873" t="n">
-        <v>-0.1304</v>
+        <v>-0.1306</v>
       </c>
       <c r="J873" t="n">
-        <v>-3.7816</v>
+        <v>-3.7874</v>
       </c>
     </row>
     <row r="874">
@@ -39149,10 +39149,10 @@
         <v>0.9</v>
       </c>
       <c r="I874" t="n">
-        <v>-0.1418</v>
+        <v>-0.1419</v>
       </c>
       <c r="J874" t="n">
-        <v>-4.1122</v>
+        <v>-4.1151</v>
       </c>
     </row>
     <row r="875">
@@ -39189,10 +39189,10 @@
         <v>0.83</v>
       </c>
       <c r="I875" t="n">
-        <v>-0.2165</v>
+        <v>-0.2167</v>
       </c>
       <c r="J875" t="n">
-        <v>-6.2785</v>
+        <v>-6.2843</v>
       </c>
     </row>
     <row r="876">
@@ -39229,10 +39229,10 @@
         <v>0.66</v>
       </c>
       <c r="I876" t="n">
-        <v>-0.3785</v>
+        <v>-0.3786</v>
       </c>
       <c r="J876" t="n">
-        <v>-10.9765</v>
+        <v>-10.9794</v>
       </c>
     </row>
     <row r="877">
@@ -39269,10 +39269,10 @@
         <v>1.52</v>
       </c>
       <c r="I877" t="n">
-        <v>1.143</v>
+        <v>1.1435</v>
       </c>
       <c r="J877" t="n">
-        <v>33.147</v>
+        <v>33.1615</v>
       </c>
     </row>
     <row r="878">
@@ -39309,10 +39309,10 @@
         <v>1.26</v>
       </c>
       <c r="I878" t="n">
-        <v>0.68</v>
+        <v>0.6805</v>
       </c>
       <c r="J878" t="n">
-        <v>19.72</v>
+        <v>19.7345</v>
       </c>
     </row>
     <row r="879">
@@ -39349,10 +39349,10 @@
         <v>1.13</v>
       </c>
       <c r="I879" t="n">
-        <v>0.3926</v>
+        <v>0.3928</v>
       </c>
       <c r="J879" t="n">
-        <v>11.3854</v>
+        <v>11.3912</v>
       </c>
     </row>
     <row r="880">
@@ -39386,13 +39386,13 @@
         <v>29</v>
       </c>
       <c r="H880" t="n">
-        <v>1</v>
+        <v>0.99</v>
       </c>
       <c r="I880" t="n">
-        <v>-0.025</v>
+        <v>-0.08450000000000001</v>
       </c>
       <c r="J880" t="n">
-        <v>-0.725</v>
+        <v>-2.4505</v>
       </c>
     </row>
     <row r="881">
@@ -39429,10 +39429,10 @@
         <v>0.85</v>
       </c>
       <c r="I881" t="n">
-        <v>-0.4987</v>
+        <v>-0.4984</v>
       </c>
       <c r="J881" t="n">
-        <v>-14.4623</v>
+        <v>-14.4536</v>
       </c>
     </row>
     <row r="882">
@@ -42266,13 +42266,13 @@
         <v>18</v>
       </c>
       <c r="H952" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="I952" t="n">
-        <v>1.2717</v>
+        <v>1.2658</v>
       </c>
       <c r="J952" t="n">
-        <v>22.8906</v>
+        <v>22.7844</v>
       </c>
     </row>
     <row r="953">
@@ -42309,10 +42309,10 @@
         <v>1.77</v>
       </c>
       <c r="I953" t="n">
-        <v>0.869</v>
+        <v>0.8693</v>
       </c>
       <c r="J953" t="n">
-        <v>15.642</v>
+        <v>15.6474</v>
       </c>
     </row>
     <row r="954">
@@ -42349,10 +42349,10 @@
         <v>0.89</v>
       </c>
       <c r="I954" t="n">
-        <v>-0.1823</v>
+        <v>-0.1822</v>
       </c>
       <c r="J954" t="n">
-        <v>-3.2814</v>
+        <v>-3.2796</v>
       </c>
     </row>
     <row r="955">
@@ -42389,10 +42389,10 @@
         <v>0.84</v>
       </c>
       <c r="I955" t="n">
-        <v>-0.2358</v>
+        <v>-0.2357</v>
       </c>
       <c r="J955" t="n">
-        <v>-4.2444</v>
+        <v>-4.2426</v>
       </c>
     </row>
     <row r="956">
@@ -42429,10 +42429,10 @@
         <v>0.71</v>
       </c>
       <c r="I956" t="n">
-        <v>-0.3607</v>
+        <v>-0.3606</v>
       </c>
       <c r="J956" t="n">
-        <v>-6.4926</v>
+        <v>-6.4908</v>
       </c>
     </row>
     <row r="957">
